--- a/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_ver_mean.xlsx
+++ b/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_ver_mean.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>41.00492337219459</v>
+        <v>3.564765393612136</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>48.88401863313852</v>
+        <v>4.733345853344402</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>88.63642219862915</v>
+        <v>8.200372503935386</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>16.66666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>118.8228140779072</v>
+        <v>11.23689695150148</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>12.5</v>
       </c>
       <c r="C6" t="n">
-        <v>152.976970260702</v>
+        <v>9.830192328925785</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>90.65045104831601</v>
+        <v>8.48312239413041</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>61.43942695519105</v>
+        <v>5.589010316467809</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>7.142857142857142</v>
       </c>
       <c r="C9" t="n">
-        <v>47.0548847202794</v>
+        <v>3.701843064748529</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" t="n">
-        <v>46.19044640039918</v>
+        <v>3.449973238260021</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>5.555555555555555</v>
       </c>
       <c r="C11" t="n">
-        <v>35.29143539460626</v>
+        <v>2.660412208883968</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>29.65654366023167</v>
+        <v>2.061638063648996</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>4.545454545454546</v>
       </c>
       <c r="C13" t="n">
-        <v>28.69675868644788</v>
+        <v>1.778151035767109</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>26.23069761953801</v>
+        <v>1.593420909178929</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>3.846153846153846</v>
       </c>
       <c r="C15" t="n">
-        <v>23.58716712707027</v>
+        <v>1.441235251271214</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>3.571428571428571</v>
       </c>
       <c r="C16" t="n">
-        <v>19.92690449781761</v>
+        <v>1.319449199324201</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>17.78138026393817</v>
+        <v>1.125796960710418</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>3.125</v>
       </c>
       <c r="C18" t="n">
-        <v>19.8523813907666</v>
+        <v>1.233734473859784</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>2.941176470588235</v>
       </c>
       <c r="C19" t="n">
-        <v>17.91307595796226</v>
+        <v>1.085850774020716</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="C20" t="n">
-        <v>15.14552739438608</v>
+        <v>0.9045920338131772</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="C21" t="n">
-        <v>11.73647102872999</v>
+        <v>0.7843461021524035</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>9.494065814372121</v>
+        <v>0.7214865976738182</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>2.380952380952381</v>
       </c>
       <c r="C23" t="n">
-        <v>7.993650082466805</v>
+        <v>0.6593620992230247</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>2.272727272727273</v>
       </c>
       <c r="C24" t="n">
-        <v>8.204335292430363</v>
+        <v>0.5833692349682001</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>2.173913043478261</v>
       </c>
       <c r="C25" t="n">
-        <v>8.097859685029649</v>
+        <v>0.5529882578880113</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>2.083333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>7.695704468853116</v>
+        <v>0.5229230319579777</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>6.928484760396893</v>
+        <v>0.4645729272633929</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>1.923076923076923</v>
       </c>
       <c r="C28" t="n">
-        <v>6.167385177267285</v>
+        <v>0.4422592035863775</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>1.851851851851852</v>
       </c>
       <c r="C29" t="n">
-        <v>5.56815649524331</v>
+        <v>0.4431051799650761</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>1.785714285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>4.865160156521583</v>
+        <v>0.413315097341471</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>1.724137931034483</v>
       </c>
       <c r="C31" t="n">
-        <v>4.530406554091909</v>
+        <v>0.3683464871219305</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>4.162317613355996</v>
+        <v>0.340530982682397</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1.612903225806452</v>
       </c>
       <c r="C33" t="n">
-        <v>4.039728647572861</v>
+        <v>0.3236898031842698</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1.5625</v>
       </c>
       <c r="C34" t="n">
-        <v>3.952385216638003</v>
+        <v>0.3019296046140088</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>1.515151515151515</v>
       </c>
       <c r="C35" t="n">
-        <v>3.742131346902548</v>
+        <v>0.2833967410642446</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>1.470588235294118</v>
       </c>
       <c r="C36" t="n">
-        <v>3.481146798789089</v>
+        <v>0.2664054484923005</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>1.428571428571428</v>
       </c>
       <c r="C37" t="n">
-        <v>3.366357810601015</v>
+        <v>0.2543642845152791</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>1.388888888888889</v>
       </c>
       <c r="C38" t="n">
-        <v>3.342091611389178</v>
+        <v>0.2579985862959115</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>1.351351351351351</v>
       </c>
       <c r="C39" t="n">
-        <v>3.142064047556392</v>
+        <v>0.2452536751363342</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="C40" t="n">
-        <v>2.954248113120578</v>
+        <v>0.2300747786520327</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>1.282051282051282</v>
       </c>
       <c r="C41" t="n">
-        <v>2.7239168586307</v>
+        <v>0.2073176695904563</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1.25</v>
       </c>
       <c r="C42" t="n">
-        <v>2.427753473037535</v>
+        <v>0.1840648843136859</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>1.219512195121951</v>
       </c>
       <c r="C43" t="n">
-        <v>2.203859810326213</v>
+        <v>0.164383050340122</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>1.19047619047619</v>
       </c>
       <c r="C44" t="n">
-        <v>2.104966193947763</v>
+        <v>0.1602585373695025</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1.162790697674419</v>
       </c>
       <c r="C45" t="n">
-        <v>2.002962157002696</v>
+        <v>0.1629618528118999</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>1.136363636363636</v>
       </c>
       <c r="C46" t="n">
-        <v>1.925879558409694</v>
+        <v>0.1576312375268999</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="C47" t="n">
-        <v>1.829537448564497</v>
+        <v>0.1478742089911377</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>1.08695652173913</v>
       </c>
       <c r="C48" t="n">
-        <v>1.768959379079576</v>
+        <v>0.1345188338747584</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>1.063829787234043</v>
       </c>
       <c r="C49" t="n">
-        <v>1.615448237371871</v>
+        <v>0.1259005418798288</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1.041666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>1.49801181909656</v>
+        <v>0.1178324323390543</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>1.020408163265306</v>
       </c>
       <c r="C51" t="n">
-        <v>1.464122983868526</v>
+        <v>0.1110932217929205</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>1.42942448168416</v>
+        <v>0.1063568881680743</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>0.9803921568627451</v>
       </c>
       <c r="C53" t="n">
-        <v>1.377810429937843</v>
+        <v>0.1020276648427742</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>0.9615384615384615</v>
       </c>
       <c r="C54" t="n">
-        <v>1.318016923157159</v>
+        <v>0.09856651356303826</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0.9433962264150942</v>
       </c>
       <c r="C55" t="n">
-        <v>1.26604479839705</v>
+        <v>0.09497058350675829</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0.9259259259259258</v>
       </c>
       <c r="C56" t="n">
-        <v>1.183797204451001</v>
+        <v>0.08953200513798663</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="C57" t="n">
-        <v>1.152135943550739</v>
+        <v>0.08710344443304952</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0.8928571428571428</v>
       </c>
       <c r="C58" t="n">
-        <v>1.114627544657461</v>
+        <v>0.08410124018837299</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>0.8771929824561403</v>
       </c>
       <c r="C59" t="n">
-        <v>1.067729296016974</v>
+        <v>0.07978236778791596</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0.8620689655172414</v>
       </c>
       <c r="C60" t="n">
-        <v>1.028841851546068</v>
+        <v>0.07636688491376709</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0.8474576271186441</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9836681464125476</v>
+        <v>0.07328727315943706</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9478167749102471</v>
+        <v>0.0711935768047874</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0.819672131147541</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9319013974244351</v>
+        <v>0.07060338604509638</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0.8064516129032259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9234784152070185</v>
+        <v>0.07043288888492187</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0.7936507936507936</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9180103138973379</v>
+        <v>0.07040359398523575</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0.78125</v>
       </c>
       <c r="C66" t="n">
-        <v>0.909843309957622</v>
+        <v>0.07007665614348549</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>0.7692307692307692</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9091050887726828</v>
+        <v>0.07056770035376347</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0.7575757575757576</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9117431802944064</v>
+        <v>0.0714993299147481</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0.7462686567164178</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9004010993782644</v>
+        <v>0.07110318428224338</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0.7352941176470588</v>
       </c>
       <c r="C70" t="n">
-        <v>0.8809711285137355</v>
+        <v>0.06995780937041636</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0.7246376811594202</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8550965901717384</v>
+        <v>0.06819718311677278</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8254411023292192</v>
+        <v>0.06592268162541326</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0.7042253521126761</v>
       </c>
       <c r="C73" t="n">
-        <v>0.7915724468314825</v>
+        <v>0.06311137045057481</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C74" t="n">
-        <v>0.7704033395474437</v>
+        <v>0.0615634808606246</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>0.684931506849315</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7440374718521481</v>
+        <v>0.05943471156246044</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0.6756756756756757</v>
       </c>
       <c r="C76" t="n">
-        <v>0.712691477809504</v>
+        <v>0.05673268840684663</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C77" t="n">
-        <v>0.679441578072324</v>
+        <v>0.05375581223420502</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6490462202830523</v>
+        <v>0.05118371261556902</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0.6493506493506493</v>
       </c>
       <c r="C79" t="n">
-        <v>0.6356356144200467</v>
+        <v>0.05052311959293926</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0.641025641025641</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6208112505053428</v>
+        <v>0.04960182307855766</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0.6329113924050632</v>
       </c>
       <c r="C81" t="n">
-        <v>0.6047740513807519</v>
+        <v>0.04845352327423935</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         <v>0.625</v>
       </c>
       <c r="C82" t="n">
-        <v>0.5888696103965253</v>
+        <v>0.04707074004897294</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0.6172839506172839</v>
       </c>
       <c r="C83" t="n">
-        <v>0.5699690351444973</v>
+        <v>0.04556259529573347</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0.6097560975609756</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5540040092917439</v>
+        <v>0.04485870631388894</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0.6024096385542168</v>
       </c>
       <c r="C85" t="n">
-        <v>0.5418950317298987</v>
+        <v>0.04467530128441569</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0.5952380952380952</v>
       </c>
       <c r="C86" t="n">
-        <v>0.5303126725139373</v>
+        <v>0.04441481522885045</v>
       </c>
     </row>
     <row r="87">
@@ -1388,7 +1388,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="C87" t="n">
-        <v>0.525117559722914</v>
+        <v>0.04405469519928739</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0.5813953488372093</v>
       </c>
       <c r="C88" t="n">
-        <v>0.5196768605203084</v>
+        <v>0.04364224555886992</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0.5747126436781609</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5175133728304473</v>
+        <v>0.04357367405258229</v>
       </c>
     </row>
     <row r="90">
@@ -1421,7 +1421,7 @@
         <v>0.5681818181818182</v>
       </c>
       <c r="C90" t="n">
-        <v>0.513634400159653</v>
+        <v>0.04333632852291498</v>
       </c>
     </row>
     <row r="91">
@@ -1432,7 +1432,7 @@
         <v>0.5617977528089888</v>
       </c>
       <c r="C91" t="n">
-        <v>0.5078024200092629</v>
+        <v>0.04290976965108803</v>
       </c>
     </row>
     <row r="92">
@@ -1443,7 +1443,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C92" t="n">
-        <v>0.4996320671614523</v>
+        <v>0.04224285216927488</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0.5494505494505494</v>
       </c>
       <c r="C93" t="n">
-        <v>0.4887387517611425</v>
+        <v>0.04129479182145197</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
         <v>0.5434782608695652</v>
       </c>
       <c r="C94" t="n">
-        <v>0.4751693278468009</v>
+        <v>0.04007002983624507</v>
       </c>
     </row>
     <row r="95">
@@ -1476,7 +1476,7 @@
         <v>0.5376344086021505</v>
       </c>
       <c r="C95" t="n">
-        <v>0.461464299560211</v>
+        <v>0.03883096362051839</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0.5319148936170213</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4472828206789705</v>
+        <v>0.03754261024444082</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="C97" t="n">
-        <v>0.4406910371590265</v>
+        <v>0.03702826862150281</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="C98" t="n">
-        <v>0.4361896386920718</v>
+        <v>0.03673055829289203</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0.5154639175257733</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4309121382191675</v>
+        <v>0.03636066986698721</v>
       </c>
     </row>
     <row r="100">
@@ -1531,7 +1531,7 @@
         <v>0.5102040816326531</v>
       </c>
       <c r="C100" t="n">
-        <v>0.424638103638108</v>
+        <v>0.03589942470820296</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0.5050505050505051</v>
       </c>
       <c r="C101" t="n">
-        <v>0.4172427030974886</v>
+        <v>0.03533703770303794</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="C102" t="n">
-        <v>0.4086686518541085</v>
+        <v>0.03479890694566268</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0.495049504950495</v>
       </c>
       <c r="C103" t="n">
-        <v>0.399010795615133</v>
+        <v>0.03425246292327483</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0.4901960784313725</v>
       </c>
       <c r="C104" t="n">
-        <v>0.388293623103679</v>
+        <v>0.03392076405440027</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0.4854368932038835</v>
       </c>
       <c r="C105" t="n">
-        <v>0.3766136481724383</v>
+        <v>0.03343905500911955</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0.4807692307692307</v>
       </c>
       <c r="C106" t="n">
-        <v>0.3641497803133613</v>
+        <v>0.03282009783528491</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="C107" t="n">
-        <v>0.3511151426574751</v>
+        <v>0.03208685350829537</v>
       </c>
     </row>
     <row r="108">
@@ -1619,7 +1619,7 @@
         <v>0.4716981132075471</v>
       </c>
       <c r="C108" t="n">
-        <v>0.3403166684148944</v>
+        <v>0.03128930852580569</v>
       </c>
     </row>
     <row r="109">
@@ -1630,7 +1630,7 @@
         <v>0.4672897196261682</v>
       </c>
       <c r="C109" t="n">
-        <v>0.3316466537537816</v>
+        <v>0.03043626197241394</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0.4629629629629629</v>
       </c>
       <c r="C110" t="n">
-        <v>0.3224617877183462</v>
+        <v>0.02955531254097589</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0.4587155963302752</v>
       </c>
       <c r="C111" t="n">
-        <v>0.3151230315127375</v>
+        <v>0.02893841465731403</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="C112" t="n">
-        <v>0.3071079165569484</v>
+        <v>0.02830821140384402</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0.4504504504504504</v>
       </c>
       <c r="C113" t="n">
-        <v>0.2991010742556868</v>
+        <v>0.0276741277856432</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0.4464285714285714</v>
       </c>
       <c r="C114" t="n">
-        <v>0.2910834384768677</v>
+        <v>0.02705463794396788</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0.4424778761061947</v>
       </c>
       <c r="C115" t="n">
-        <v>0.2859839186489377</v>
+        <v>0.02675567077967656</v>
       </c>
     </row>
     <row r="116">
@@ -1707,7 +1707,7 @@
         <v>0.4385964912280702</v>
       </c>
       <c r="C116" t="n">
-        <v>0.2816281433423736</v>
+        <v>0.02653475373703525</v>
       </c>
     </row>
     <row r="117">
@@ -1718,7 +1718,7 @@
         <v>0.4347826086956521</v>
       </c>
       <c r="C117" t="n">
-        <v>0.2765089135590866</v>
+        <v>0.0262403990506392</v>
       </c>
     </row>
     <row r="118">
@@ -1729,7 +1729,7 @@
         <v>0.4310344827586207</v>
       </c>
       <c r="C118" t="n">
-        <v>0.2708714972472294</v>
+        <v>0.02588673410100339</v>
       </c>
     </row>
     <row r="119">
@@ -1740,7 +1740,7 @@
         <v>0.4273504273504274</v>
       </c>
       <c r="C119" t="n">
-        <v>0.2658060954223867</v>
+        <v>0.02548291318845224</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0.4237288135593221</v>
       </c>
       <c r="C120" t="n">
-        <v>0.2613025432262336</v>
+        <v>0.02504130404515697</v>
       </c>
     </row>
     <row r="121">
@@ -1762,7 +1762,7 @@
         <v>0.4201680672268908</v>
       </c>
       <c r="C121" t="n">
-        <v>0.2563675791251068</v>
+        <v>0.02457129043886592</v>
       </c>
     </row>
     <row r="122">
@@ -1773,7 +1773,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="C122" t="n">
-        <v>0.2510852474217686</v>
+        <v>0.02408269926507457</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0.4132231404958678</v>
       </c>
       <c r="C123" t="n">
-        <v>0.2462713257356589</v>
+        <v>0.02365929160882489</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0.4098360655737705</v>
       </c>
       <c r="C124" t="n">
-        <v>0.2412832349385368</v>
+        <v>0.02323555246916697</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0.4065040650406504</v>
       </c>
       <c r="C125" t="n">
-        <v>0.2371759560107427</v>
+        <v>0.02296297537751572</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0.4032258064516129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.2363062608520538</v>
+        <v>0.02308842865503759</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0.4</v>
       </c>
       <c r="C127" t="n">
-        <v>0.237373104747313</v>
+        <v>0.02319554494076294</v>
       </c>
     </row>
     <row r="128">
@@ -1839,7 +1839,7 @@
         <v>0.3968253968253968</v>
       </c>
       <c r="C128" t="n">
-        <v>0.2388364491810173</v>
+        <v>0.02327747238348559</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0.3937007874015748</v>
       </c>
       <c r="C129" t="n">
-        <v>0.2407071672811077</v>
+        <v>0.02335483288750521</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0.390625</v>
       </c>
       <c r="C130" t="n">
-        <v>0.2425340190608871</v>
+        <v>0.02340732164503582</v>
       </c>
     </row>
     <row r="131">
@@ -1872,7 +1872,7 @@
         <v>0.3875968992248062</v>
       </c>
       <c r="C131" t="n">
-        <v>0.2441295451015641</v>
+        <v>0.0234256390575412</v>
       </c>
     </row>
     <row r="132">
@@ -1883,7 +1883,7 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="C132" t="n">
-        <v>0.2453814058344051</v>
+        <v>0.0234080869582726</v>
       </c>
     </row>
     <row r="133">
@@ -1894,7 +1894,7 @@
         <v>0.3816793893129771</v>
       </c>
       <c r="C133" t="n">
-        <v>0.2461915660690339</v>
+        <v>0.02335366262530482</v>
       </c>
     </row>
     <row r="134">
@@ -1905,7 +1905,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>0.2466709985352111</v>
+        <v>0.02326085008821354</v>
       </c>
     </row>
     <row r="135">
@@ -1916,7 +1916,7 @@
         <v>0.3759398496240601</v>
       </c>
       <c r="C135" t="n">
-        <v>0.2466793792176629</v>
+        <v>0.02313139391660546</v>
       </c>
     </row>
     <row r="136">
@@ -1927,7 +1927,7 @@
         <v>0.3731343283582089</v>
       </c>
       <c r="C136" t="n">
-        <v>0.2460949177104196</v>
+        <v>0.02296695739543247</v>
       </c>
     </row>
     <row r="137">
@@ -1938,7 +1938,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="C137" t="n">
-        <v>0.2449610807644828</v>
+        <v>0.02277613764752549</v>
       </c>
     </row>
     <row r="138">
@@ -1949,7 +1949,7 @@
         <v>0.3676470588235294</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2437627547441036</v>
+        <v>0.02261096074503104</v>
       </c>
     </row>
     <row r="139">
@@ -1960,7 +1960,7 @@
         <v>0.364963503649635</v>
       </c>
       <c r="C139" t="n">
-        <v>0.2430362349220471</v>
+        <v>0.02252563921993438</v>
       </c>
     </row>
     <row r="140">
@@ -1971,7 +1971,7 @@
         <v>0.3623188405797101</v>
       </c>
       <c r="C140" t="n">
-        <v>0.2415688654843096</v>
+        <v>0.02239483209998509</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0.3597122302158273</v>
       </c>
       <c r="C141" t="n">
-        <v>0.2393831867124314</v>
+        <v>0.02222207499225756</v>
       </c>
     </row>
     <row r="142">
@@ -1993,7 +1993,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="C142" t="n">
-        <v>0.2369939899499533</v>
+        <v>0.02201101209550037</v>
       </c>
     </row>
     <row r="143">
@@ -2004,7 +2004,7 @@
         <v>0.3546099290780142</v>
       </c>
       <c r="C143" t="n">
-        <v>0.2347639053857495</v>
+        <v>0.021766388364925</v>
       </c>
     </row>
     <row r="144">
@@ -2015,7 +2015,7 @@
         <v>0.3521126760563381</v>
       </c>
       <c r="C144" t="n">
-        <v>0.2332093388648391</v>
+        <v>0.02149190866383075</v>
       </c>
     </row>
     <row r="145">
@@ -2026,7 +2026,7 @@
         <v>0.3496503496503497</v>
       </c>
       <c r="C145" t="n">
-        <v>0.2314316229050688</v>
+        <v>0.02119155099373097</v>
       </c>
     </row>
     <row r="146">
@@ -2037,7 +2037,7 @@
         <v>0.3472222222222222</v>
       </c>
       <c r="C146" t="n">
-        <v>0.2299518230011544</v>
+        <v>0.02093292906723415</v>
       </c>
     </row>
     <row r="147">
@@ -2048,7 +2048,7 @@
         <v>0.3448275862068966</v>
       </c>
       <c r="C147" t="n">
-        <v>0.2285411465928822</v>
+        <v>0.0206912883337945</v>
       </c>
     </row>
     <row r="148">
@@ -2059,7 +2059,7 @@
         <v>0.3424657534246575</v>
       </c>
       <c r="C148" t="n">
-        <v>0.2273777327275257</v>
+        <v>0.02050443423201534</v>
       </c>
     </row>
     <row r="149">
@@ -2070,7 +2070,7 @@
         <v>0.3401360544217687</v>
       </c>
       <c r="C149" t="n">
-        <v>0.2272589736367379</v>
+        <v>0.02039046227130056</v>
       </c>
     </row>
     <row r="150">
@@ -2081,7 +2081,7 @@
         <v>0.3378378378378378</v>
       </c>
       <c r="C150" t="n">
-        <v>0.227591107690388</v>
+        <v>0.02023763188739779</v>
       </c>
     </row>
     <row r="151">
@@ -2092,7 +2092,7 @@
         <v>0.3355704697986577</v>
       </c>
       <c r="C151" t="n">
-        <v>0.2274336681493021</v>
+        <v>0.0200897983662292</v>
       </c>
     </row>
     <row r="152">
@@ -2103,7 +2103,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C152" t="n">
-        <v>0.2270175834132066</v>
+        <v>0.01997165664043023</v>
       </c>
     </row>
     <row r="153">
@@ -2114,7 +2114,7 @@
         <v>0.3311258278145696</v>
       </c>
       <c r="C153" t="n">
-        <v>0.2271891333265047</v>
+        <v>0.0199964275755351</v>
       </c>
     </row>
     <row r="154">
@@ -2125,7 +2125,7 @@
         <v>0.3289473684210527</v>
       </c>
       <c r="C154" t="n">
-        <v>0.227145446067498</v>
+        <v>0.02001165740605542</v>
       </c>
     </row>
     <row r="155">
@@ -2136,7 +2136,7 @@
         <v>0.326797385620915</v>
       </c>
       <c r="C155" t="n">
-        <v>0.226741926395638</v>
+        <v>0.01999772283426317</v>
       </c>
     </row>
     <row r="156">
@@ -2147,7 +2147,7 @@
         <v>0.3246753246753247</v>
       </c>
       <c r="C156" t="n">
-        <v>0.2262891317373116</v>
+        <v>0.01998211863318117</v>
       </c>
     </row>
     <row r="157">
@@ -2158,7 +2158,7 @@
         <v>0.3225806451612903</v>
       </c>
       <c r="C157" t="n">
-        <v>0.2256049059117049</v>
+        <v>0.01994485780044623</v>
       </c>
     </row>
     <row r="158">
@@ -2169,7 +2169,7 @@
         <v>0.3205128205128205</v>
       </c>
       <c r="C158" t="n">
-        <v>0.2247671224990333</v>
+        <v>0.02008609860677314</v>
       </c>
     </row>
     <row r="159">
@@ -2180,7 +2180,7 @@
         <v>0.3184713375796178</v>
       </c>
       <c r="C159" t="n">
-        <v>0.2248915782301941</v>
+        <v>0.02022154857827121</v>
       </c>
     </row>
     <row r="160">
@@ -2191,7 +2191,7 @@
         <v>0.3164556962025316</v>
       </c>
       <c r="C160" t="n">
-        <v>0.225099589877504</v>
+        <v>0.02029019311933923</v>
       </c>
     </row>
     <row r="161">
@@ -2202,7 +2202,7 @@
         <v>0.3144654088050314</v>
       </c>
       <c r="C161" t="n">
-        <v>0.2256977339531749</v>
+        <v>0.02029411147882269</v>
       </c>
     </row>
     <row r="162">
@@ -2213,7 +2213,7 @@
         <v>0.3125</v>
       </c>
       <c r="C162" t="n">
-        <v>0.2265380272142247</v>
+        <v>0.02026675132350964</v>
       </c>
     </row>
     <row r="163">
@@ -2224,7 +2224,7 @@
         <v>0.3105590062111801</v>
       </c>
       <c r="C163" t="n">
-        <v>0.2273282749316758</v>
+        <v>0.02021523283750896</v>
       </c>
     </row>
     <row r="164">
@@ -2235,7 +2235,7 @@
         <v>0.308641975308642</v>
       </c>
       <c r="C164" t="n">
-        <v>0.2280495920041071</v>
+        <v>0.02010833472327761</v>
       </c>
     </row>
     <row r="165">
@@ -2246,7 +2246,7 @@
         <v>0.3067484662576687</v>
       </c>
       <c r="C165" t="n">
-        <v>0.2286942203464181</v>
+        <v>0.02007806638400801</v>
       </c>
     </row>
     <row r="166">
@@ -2257,7 +2257,7 @@
         <v>0.3048780487804878</v>
       </c>
       <c r="C166" t="n">
-        <v>0.2292539854349797</v>
+        <v>0.02001704092757884</v>
       </c>
     </row>
     <row r="167">
@@ -2268,7 +2268,7 @@
         <v>0.303030303030303</v>
       </c>
       <c r="C167" t="n">
-        <v>0.230208211018422</v>
+        <v>0.01997654383653272</v>
       </c>
     </row>
     <row r="168">
@@ -2279,7 +2279,7 @@
         <v>0.3012048192771084</v>
       </c>
       <c r="C168" t="n">
-        <v>0.2310077105570482</v>
+        <v>0.01990337630138173</v>
       </c>
     </row>
     <row r="169">
@@ -2290,7 +2290,7 @@
         <v>0.2994011976047904</v>
       </c>
       <c r="C169" t="n">
-        <v>0.2320157216820634</v>
+        <v>0.01983662383982587</v>
       </c>
     </row>
     <row r="170">
@@ -2301,7 +2301,7 @@
         <v>0.2976190476190476</v>
       </c>
       <c r="C170" t="n">
-        <v>0.2329369180345151</v>
+        <v>0.01975178942516221</v>
       </c>
     </row>
     <row r="171">
@@ -2312,7 +2312,7 @@
         <v>0.2958579881656805</v>
       </c>
       <c r="C171" t="n">
-        <v>0.2336233477155886</v>
+        <v>0.0196348245353211</v>
       </c>
     </row>
     <row r="172">
@@ -2323,7 +2323,7 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="C172" t="n">
-        <v>0.2340636445319757</v>
+        <v>0.01948734866548988</v>
       </c>
     </row>
     <row r="173">
@@ -2334,7 +2334,7 @@
         <v>0.2923976608187134</v>
       </c>
       <c r="C173" t="n">
-        <v>0.2351496647453774</v>
+        <v>0.01935234024223181</v>
       </c>
     </row>
     <row r="174">
@@ -2345,7 +2345,7 @@
         <v>0.2906976744186047</v>
       </c>
       <c r="C174" t="n">
-        <v>0.2363204069337843</v>
+        <v>0.01931102276550989</v>
       </c>
     </row>
     <row r="175">
@@ -2356,7 +2356,7 @@
         <v>0.2890173410404624</v>
       </c>
       <c r="C175" t="n">
-        <v>0.2371924024310262</v>
+        <v>0.01928453658221288</v>
       </c>
     </row>
     <row r="176">
@@ -2367,7 +2367,7 @@
         <v>0.2873563218390804</v>
       </c>
       <c r="C176" t="n">
-        <v>0.2377504577409796</v>
+        <v>0.0192264016921349</v>
       </c>
     </row>
     <row r="177">
@@ -2378,7 +2378,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="C177" t="n">
-        <v>0.2380072982248747</v>
+        <v>0.01913814798402608</v>
       </c>
     </row>
     <row r="178">
@@ -2389,7 +2389,7 @@
         <v>0.2840909090909091</v>
       </c>
       <c r="C178" t="n">
-        <v>0.2381126099485811</v>
+        <v>0.01902732599647406</v>
       </c>
     </row>
     <row r="179">
@@ -2400,7 +2400,7 @@
         <v>0.2824858757062147</v>
       </c>
       <c r="C179" t="n">
-        <v>0.2379686157707948</v>
+        <v>0.01889606092530108</v>
       </c>
     </row>
     <row r="180">
@@ -2411,7 +2411,7 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="C180" t="n">
-        <v>0.2380008896700011</v>
+        <v>0.01878860792307567</v>
       </c>
     </row>
     <row r="181">
@@ -2422,7 +2422,7 @@
         <v>0.2793296089385475</v>
       </c>
       <c r="C181" t="n">
-        <v>0.2376716401911159</v>
+        <v>0.01865129762225964</v>
       </c>
     </row>
     <row r="182">
@@ -2433,7 +2433,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="C182" t="n">
-        <v>0.2369767063768602</v>
+        <v>0.01848450806705982</v>
       </c>
     </row>
     <row r="183">
@@ -2444,7 +2444,7 @@
         <v>0.2762430939226519</v>
       </c>
       <c r="C183" t="n">
-        <v>0.2361050342092882</v>
+        <v>0.01829078593977986</v>
       </c>
     </row>
     <row r="184">
@@ -2455,7 +2455,7 @@
         <v>0.2747252747252747</v>
       </c>
       <c r="C184" t="n">
-        <v>0.2349106651118833</v>
+        <v>0.01807118541761242</v>
       </c>
     </row>
     <row r="185">
@@ -2466,7 +2466,7 @@
         <v>0.273224043715847</v>
       </c>
       <c r="C185" t="n">
-        <v>0.2351469289222168</v>
+        <v>0.0178273738341801</v>
       </c>
     </row>
     <row r="186">
@@ -2477,7 +2477,7 @@
         <v>0.2717391304347826</v>
       </c>
       <c r="C186" t="n">
-        <v>0.2352598052778014</v>
+        <v>0.01756116515214828</v>
       </c>
     </row>
     <row r="187">
@@ -2488,7 +2488,7 @@
         <v>0.2702702702702702</v>
       </c>
       <c r="C187" t="n">
-        <v>0.2350229851503919</v>
+        <v>0.0173000343909479</v>
       </c>
     </row>
     <row r="188">
@@ -2499,7 +2499,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="C188" t="n">
-        <v>0.2344346585807991</v>
+        <v>0.017034434813095</v>
       </c>
     </row>
     <row r="189">
@@ -2510,7 +2510,7 @@
         <v>0.267379679144385</v>
       </c>
       <c r="C189" t="n">
-        <v>0.2337246998398708</v>
+        <v>0.016771579896958</v>
       </c>
     </row>
     <row r="190">
@@ -2521,7 +2521,7 @@
         <v>0.2659574468085106</v>
       </c>
       <c r="C190" t="n">
-        <v>0.2327462228358695</v>
+        <v>0.01649493312188802</v>
       </c>
     </row>
     <row r="191">
@@ -2532,7 +2532,7 @@
         <v>0.2645502645502645</v>
       </c>
       <c r="C191" t="n">
-        <v>0.2315189959963535</v>
+        <v>0.01623756718319663</v>
       </c>
     </row>
     <row r="192">
@@ -2543,7 +2543,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="C192" t="n">
-        <v>0.2301475902373651</v>
+        <v>0.01603539101006467</v>
       </c>
     </row>
     <row r="193">
@@ -2554,7 +2554,7 @@
         <v>0.2617801047120419</v>
       </c>
       <c r="C193" t="n">
-        <v>0.2295319379557327</v>
+        <v>0.01582604179618566</v>
       </c>
     </row>
     <row r="194">
@@ -2565,7 +2565,7 @@
         <v>0.2604166666666667</v>
       </c>
       <c r="C194" t="n">
-        <v>0.2292494190444871</v>
+        <v>0.0156690547009347</v>
       </c>
     </row>
     <row r="195">
@@ -2576,7 +2576,7 @@
         <v>0.2590673575129534</v>
       </c>
       <c r="C195" t="n">
-        <v>0.2292969391229826</v>
+        <v>0.01552010626933774</v>
       </c>
     </row>
     <row r="196">
@@ -2587,7 +2587,7 @@
         <v>0.2577319587628866</v>
       </c>
       <c r="C196" t="n">
-        <v>0.2290813113707639</v>
+        <v>0.01535522161153422</v>
       </c>
     </row>
     <row r="197">
@@ -2598,7 +2598,7 @@
         <v>0.2564102564102564</v>
       </c>
       <c r="C197" t="n">
-        <v>0.2286057736604061</v>
+        <v>0.01518333468487445</v>
       </c>
     </row>
     <row r="198">
@@ -2609,7 +2609,7 @@
         <v>0.2551020408163265</v>
       </c>
       <c r="C198" t="n">
-        <v>0.2278751377851162</v>
+        <v>0.01500408571600318</v>
       </c>
     </row>
     <row r="199">
@@ -2620,7 +2620,7 @@
         <v>0.2538071065989848</v>
       </c>
       <c r="C199" t="n">
-        <v>0.2269945693414438</v>
+        <v>0.01482319270477853</v>
       </c>
     </row>
     <row r="200">
@@ -2631,7 +2631,7 @@
         <v>0.2525252525252525</v>
       </c>
       <c r="C200" t="n">
-        <v>0.2260673522718615</v>
+        <v>0.01465079843369416</v>
       </c>
     </row>
     <row r="201">
@@ -2642,7 +2642,7 @@
         <v>0.2512562814070352</v>
       </c>
       <c r="C201" t="n">
-        <v>0.2250491194958705</v>
+        <v>0.01448423920447853</v>
       </c>
     </row>
     <row r="202">
@@ -2653,7 +2653,7 @@
         <v>0.25</v>
       </c>
       <c r="C202" t="n">
-        <v>0.223944662725399</v>
+        <v>0.01432505098895256</v>
       </c>
     </row>
   </sheetData>

--- a/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_ver_mean.xlsx
+++ b/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_ver_mean.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3.564765393612136</v>
+        <v>3.944278404343558</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>4.733345853344402</v>
+        <v>5.020951023523922</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>8.200372503935386</v>
+        <v>7.675290215436156</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>16.66666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>11.23689695150148</v>
+        <v>11.6596670888235</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>12.5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.830192328925785</v>
+        <v>15.80739756358043</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>8.48312239413041</v>
+        <v>10.4637809880078</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>5.589010316467809</v>
+        <v>7.360057094019317</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>7.142857142857142</v>
       </c>
       <c r="C9" t="n">
-        <v>3.701843064748529</v>
+        <v>5.897360078026272</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" t="n">
-        <v>3.449973238260021</v>
+        <v>6.033852197861362</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>5.555555555555555</v>
       </c>
       <c r="C11" t="n">
-        <v>2.660412208883968</v>
+        <v>4.363397941888826</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>2.061638063648996</v>
+        <v>3.826308280088305</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>4.545454545454546</v>
       </c>
       <c r="C13" t="n">
-        <v>1.778151035767109</v>
+        <v>3.588607811170709</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>1.593420909178929</v>
+        <v>2.871675091408207</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>3.846153846153846</v>
       </c>
       <c r="C15" t="n">
-        <v>1.441235251271214</v>
+        <v>2.502206383384906</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>3.571428571428571</v>
       </c>
       <c r="C16" t="n">
-        <v>1.319449199324201</v>
+        <v>2.498872230571417</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>1.125796960710418</v>
+        <v>2.163546433668063</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>3.125</v>
       </c>
       <c r="C18" t="n">
-        <v>1.233734473859784</v>
+        <v>2.300110800826814</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>2.941176470588235</v>
       </c>
       <c r="C19" t="n">
-        <v>1.085850774020716</v>
+        <v>2.158780549186609</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9045920338131772</v>
+        <v>1.850372169505014</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7843461021524035</v>
+        <v>1.60565589383257</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7214865976738182</v>
+        <v>1.392160553910644</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>2.380952380952381</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6593620992230247</v>
+        <v>1.251156389097175</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>2.272727272727273</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5833692349682001</v>
+        <v>1.172423603775509</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>2.173913043478261</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5529882578880113</v>
+        <v>1.06175636003646</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>2.083333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5229230319579777</v>
+        <v>0.9912713660825129</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4645729272633929</v>
+        <v>0.9101149360215238</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>1.923076923076923</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4422592035863775</v>
+        <v>0.8285789211658626</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>1.851851851851852</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4431051799650761</v>
+        <v>0.7946575053454421</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>1.785714285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>0.413315097341471</v>
+        <v>0.6996995822866132</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>1.724137931034483</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3683464871219305</v>
+        <v>0.6314833186472916</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>0.340530982682397</v>
+        <v>0.5763947580127076</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1.612903225806452</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3236898031842698</v>
+        <v>0.567699481684703</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1.5625</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3019296046140088</v>
+        <v>0.5478225508109025</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>1.515151515151515</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2833967410642446</v>
+        <v>0.5123264033926819</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>1.470588235294118</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2664054484923005</v>
+        <v>0.4756575644765453</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>1.428571428571428</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2543642845152791</v>
+        <v>0.45306350026708</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>1.388888888888889</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2579985862959115</v>
+        <v>0.4302738799611929</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>1.351351351351351</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2452536751363342</v>
+        <v>0.398076418386218</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2300747786520327</v>
+        <v>0.3736245905664139</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>1.282051282051282</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2073176695904563</v>
+        <v>0.3501797157743412</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1.25</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1840648843136859</v>
+        <v>0.3196253522720414</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>1.219512195121951</v>
       </c>
       <c r="C43" t="n">
-        <v>0.164383050340122</v>
+        <v>0.2942393848814595</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>1.19047619047619</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1602585373695025</v>
+        <v>0.279111903311076</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1.162790697674419</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1629618528118999</v>
+        <v>0.2780644049172107</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>1.136363636363636</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1576312375268999</v>
+        <v>0.2783210284396055</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1478742089911377</v>
+        <v>0.2696257073641956</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>1.08695652173913</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1345188338747584</v>
+        <v>0.2549489937252481</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>1.063829787234043</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1259005418798288</v>
+        <v>0.2348044756320157</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1.041666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1178324323390543</v>
+        <v>0.2161347281267111</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>1.020408163265306</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1110932217929205</v>
+        <v>0.2048904111846375</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1063568881680743</v>
+        <v>0.1929719239822753</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>0.9803921568627451</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1020276648427742</v>
+        <v>0.1785047579320738</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>0.9615384615384615</v>
       </c>
       <c r="C54" t="n">
-        <v>0.09856651356303826</v>
+        <v>0.1620877178941875</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0.9433962264150942</v>
       </c>
       <c r="C55" t="n">
-        <v>0.09497058350675829</v>
+        <v>0.148206660281184</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0.9259259259259258</v>
       </c>
       <c r="C56" t="n">
-        <v>0.08953200513798663</v>
+        <v>0.1348378257281491</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="C57" t="n">
-        <v>0.08710344443304952</v>
+        <v>0.1292632381765661</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0.8928571428571428</v>
       </c>
       <c r="C58" t="n">
-        <v>0.08410124018837299</v>
+        <v>0.1251533911799537</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>0.8771929824561403</v>
       </c>
       <c r="C59" t="n">
-        <v>0.07978236778791596</v>
+        <v>0.1204902151409818</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0.8620689655172414</v>
       </c>
       <c r="C60" t="n">
-        <v>0.07636688491376709</v>
+        <v>0.1161231457398282</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0.8474576271186441</v>
       </c>
       <c r="C61" t="n">
-        <v>0.07328727315943706</v>
+        <v>0.1118659910646052</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0711935768047874</v>
+        <v>0.1079232139516871</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0.819672131147541</v>
       </c>
       <c r="C63" t="n">
-        <v>0.07060338604509638</v>
+        <v>0.1043574688553683</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0.8064516129032259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.07043288888492187</v>
+        <v>0.1005989201783777</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0.7936507936507936</v>
       </c>
       <c r="C65" t="n">
-        <v>0.07040359398523575</v>
+        <v>0.09675746369736624</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0.78125</v>
       </c>
       <c r="C66" t="n">
-        <v>0.07007665614348549</v>
+        <v>0.09301195429596422</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>0.7692307692307692</v>
       </c>
       <c r="C67" t="n">
-        <v>0.07056770035376347</v>
+        <v>0.08983466812940215</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0.7575757575757576</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0714993299147481</v>
+        <v>0.08679284950670739</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0.7462686567164178</v>
       </c>
       <c r="C69" t="n">
-        <v>0.07110318428224338</v>
+        <v>0.08393245526599982</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0.7352941176470588</v>
       </c>
       <c r="C70" t="n">
-        <v>0.06995780937041636</v>
+        <v>0.08127204471765409</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0.7246376811594202</v>
       </c>
       <c r="C71" t="n">
-        <v>0.06819718311677278</v>
+        <v>0.07947015951263267</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="C72" t="n">
-        <v>0.06592268162541326</v>
+        <v>0.07802326366899159</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0.7042253521126761</v>
       </c>
       <c r="C73" t="n">
-        <v>0.06311137045057481</v>
+        <v>0.0764377435430679</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0615634808606246</v>
+        <v>0.07457803453663694</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>0.684931506849315</v>
       </c>
       <c r="C75" t="n">
-        <v>0.05943471156246044</v>
+        <v>0.07249504644142653</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0.6756756756756757</v>
       </c>
       <c r="C76" t="n">
-        <v>0.05673268840684663</v>
+        <v>0.07100258457344531</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C77" t="n">
-        <v>0.05375581223420502</v>
+        <v>0.06954661807104259</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05118371261556902</v>
+        <v>0.06840896459535262</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0.6493506493506493</v>
       </c>
       <c r="C79" t="n">
-        <v>0.05052311959293926</v>
+        <v>0.06750518342048371</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0.641025641025641</v>
       </c>
       <c r="C80" t="n">
-        <v>0.04960182307855766</v>
+        <v>0.06653145042423626</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0.6329113924050632</v>
       </c>
       <c r="C81" t="n">
-        <v>0.04845352327423935</v>
+        <v>0.065476223792761</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         <v>0.625</v>
       </c>
       <c r="C82" t="n">
-        <v>0.04707074004897294</v>
+        <v>0.06447355159940323</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0.6172839506172839</v>
       </c>
       <c r="C83" t="n">
-        <v>0.04556259529573347</v>
+        <v>0.0630910293164991</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0.6097560975609756</v>
       </c>
       <c r="C84" t="n">
-        <v>0.04485870631388894</v>
+        <v>0.06187639648545896</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0.6024096385542168</v>
       </c>
       <c r="C85" t="n">
-        <v>0.04467530128441569</v>
+        <v>0.06087972863756826</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0.5952380952380952</v>
       </c>
       <c r="C86" t="n">
-        <v>0.04441481522885045</v>
+        <v>0.0597493171955976</v>
       </c>
     </row>
     <row r="87">
@@ -1388,7 +1388,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="C87" t="n">
-        <v>0.04405469519928739</v>
+        <v>0.05909432295496605</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0.5813953488372093</v>
       </c>
       <c r="C88" t="n">
-        <v>0.04364224555886992</v>
+        <v>0.05820982549005007</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0.5747126436781609</v>
       </c>
       <c r="C89" t="n">
-        <v>0.04357367405258229</v>
+        <v>0.05707246599837611</v>
       </c>
     </row>
     <row r="90">
@@ -1421,7 +1421,7 @@
         <v>0.5681818181818182</v>
       </c>
       <c r="C90" t="n">
-        <v>0.04333632852291498</v>
+        <v>0.05571568702921632</v>
       </c>
     </row>
     <row r="91">
@@ -1432,7 +1432,7 @@
         <v>0.5617977528089888</v>
       </c>
       <c r="C91" t="n">
-        <v>0.04290976965108803</v>
+        <v>0.05417609992965031</v>
       </c>
     </row>
     <row r="92">
@@ -1443,7 +1443,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C92" t="n">
-        <v>0.04224285216927488</v>
+        <v>0.05249803841995235</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0.5494505494505494</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04129479182145197</v>
+        <v>0.05081127175902615</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
         <v>0.5434782608695652</v>
       </c>
       <c r="C94" t="n">
-        <v>0.04007002983624507</v>
+        <v>0.0496359938103669</v>
       </c>
     </row>
     <row r="95">
@@ -1476,7 +1476,7 @@
         <v>0.5376344086021505</v>
       </c>
       <c r="C95" t="n">
-        <v>0.03883096362051839</v>
+        <v>0.04843081148454349</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0.5319148936170213</v>
       </c>
       <c r="C96" t="n">
-        <v>0.03754261024444082</v>
+        <v>0.04720048088038863</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="C97" t="n">
-        <v>0.03702826862150281</v>
+        <v>0.04592626185523781</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="C98" t="n">
-        <v>0.03673055829289203</v>
+        <v>0.04462470652280688</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0.5154639175257733</v>
       </c>
       <c r="C99" t="n">
-        <v>0.03636066986698721</v>
+        <v>0.04331123454096408</v>
       </c>
     </row>
     <row r="100">
@@ -1531,7 +1531,7 @@
         <v>0.5102040816326531</v>
       </c>
       <c r="C100" t="n">
-        <v>0.03589942470820296</v>
+        <v>0.04199726613491252</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0.5050505050505051</v>
       </c>
       <c r="C101" t="n">
-        <v>0.03533703770303794</v>
+        <v>0.04069356421414314</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="C102" t="n">
-        <v>0.03479890694566268</v>
+        <v>0.03940916274217949</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0.495049504950495</v>
       </c>
       <c r="C103" t="n">
-        <v>0.03425246292327483</v>
+        <v>0.03815151151213785</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0.4901960784313725</v>
       </c>
       <c r="C104" t="n">
-        <v>0.03392076405440027</v>
+        <v>0.03727339924948441</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0.4854368932038835</v>
       </c>
       <c r="C105" t="n">
-        <v>0.03343905500911955</v>
+        <v>0.03640310394040151</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0.4807692307692307</v>
       </c>
       <c r="C106" t="n">
-        <v>0.03282009783528491</v>
+        <v>0.03553713017608547</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="C107" t="n">
-        <v>0.03208685350829537</v>
+        <v>0.03467806240170505</v>
       </c>
     </row>
     <row r="108">
@@ -1619,7 +1619,7 @@
         <v>0.4716981132075471</v>
       </c>
       <c r="C108" t="n">
-        <v>0.03128930852580569</v>
+        <v>0.03408677395618948</v>
       </c>
     </row>
     <row r="109">
@@ -1630,7 +1630,7 @@
         <v>0.4672897196261682</v>
       </c>
       <c r="C109" t="n">
-        <v>0.03043626197241394</v>
+        <v>0.03373498123082606</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0.4629629629629629</v>
       </c>
       <c r="C110" t="n">
-        <v>0.02955531254097589</v>
+        <v>0.03333502712933775</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0.4587155963302752</v>
       </c>
       <c r="C111" t="n">
-        <v>0.02893841465731403</v>
+        <v>0.03310867471878388</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="C112" t="n">
-        <v>0.02830821140384402</v>
+        <v>0.03278221192053979</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0.4504504504504504</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0276741277856432</v>
+        <v>0.03241168819511638</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0.4464285714285714</v>
       </c>
       <c r="C114" t="n">
-        <v>0.02705463794396788</v>
+        <v>0.0319845571163179</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0.4424778761061947</v>
       </c>
       <c r="C115" t="n">
-        <v>0.02675567077967656</v>
+        <v>0.03156369919206451</v>
       </c>
     </row>
     <row r="116">
@@ -1707,7 +1707,7 @@
         <v>0.4385964912280702</v>
       </c>
       <c r="C116" t="n">
-        <v>0.02653475373703525</v>
+        <v>0.031230907827427</v>
       </c>
     </row>
     <row r="117">
@@ -1718,7 +1718,7 @@
         <v>0.4347826086956521</v>
       </c>
       <c r="C117" t="n">
-        <v>0.0262403990506392</v>
+        <v>0.03086455651118517</v>
       </c>
     </row>
     <row r="118">
@@ -1729,7 +1729,7 @@
         <v>0.4310344827586207</v>
       </c>
       <c r="C118" t="n">
-        <v>0.02588673410100339</v>
+        <v>0.03048290422484105</v>
       </c>
     </row>
     <row r="119">
@@ -1740,7 +1740,7 @@
         <v>0.4273504273504274</v>
       </c>
       <c r="C119" t="n">
-        <v>0.02548291318845224</v>
+        <v>0.03039004282314444</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0.4237288135593221</v>
       </c>
       <c r="C120" t="n">
-        <v>0.02504130404515697</v>
+        <v>0.03038764103076888</v>
       </c>
     </row>
     <row r="121">
@@ -1762,7 +1762,7 @@
         <v>0.4201680672268908</v>
       </c>
       <c r="C121" t="n">
-        <v>0.02457129043886592</v>
+        <v>0.03035605321489763</v>
       </c>
     </row>
     <row r="122">
@@ -1773,7 +1773,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="C122" t="n">
-        <v>0.02408269926507457</v>
+        <v>0.0302946046547351</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0.4132231404958678</v>
       </c>
       <c r="C123" t="n">
-        <v>0.02365929160882489</v>
+        <v>0.03020101516944925</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0.4098360655737705</v>
       </c>
       <c r="C124" t="n">
-        <v>0.02323555246916697</v>
+        <v>0.030072677403433</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0.4065040650406504</v>
       </c>
       <c r="C125" t="n">
-        <v>0.02296297537751572</v>
+        <v>0.02991623019302811</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0.4032258064516129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.02308842865503759</v>
+        <v>0.02995155419958708</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0.4</v>
       </c>
       <c r="C127" t="n">
-        <v>0.02319554494076294</v>
+        <v>0.03016375204733994</v>
       </c>
     </row>
     <row r="128">
@@ -1839,7 +1839,7 @@
         <v>0.3968253968253968</v>
       </c>
       <c r="C128" t="n">
-        <v>0.02327747238348559</v>
+        <v>0.03040065051785558</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0.3937007874015748</v>
       </c>
       <c r="C129" t="n">
-        <v>0.02335483288750521</v>
+        <v>0.03066743469714051</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0.390625</v>
       </c>
       <c r="C130" t="n">
-        <v>0.02340732164503582</v>
+        <v>0.03092140856179061</v>
       </c>
     </row>
     <row r="131">
@@ -1872,7 +1872,7 @@
         <v>0.3875968992248062</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0234256390575412</v>
+        <v>0.03114599099367791</v>
       </c>
     </row>
     <row r="132">
@@ -1883,7 +1883,7 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0234080869582726</v>
+        <v>0.03133151695580981</v>
       </c>
     </row>
     <row r="133">
@@ -1894,7 +1894,7 @@
         <v>0.3816793893129771</v>
       </c>
       <c r="C133" t="n">
-        <v>0.02335366262530482</v>
+        <v>0.03146909574005762</v>
       </c>
     </row>
     <row r="134">
@@ -1905,7 +1905,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>0.02326085008821354</v>
+        <v>0.03157053424799306</v>
       </c>
     </row>
     <row r="135">
@@ -1916,7 +1916,7 @@
         <v>0.3759398496240601</v>
       </c>
       <c r="C135" t="n">
-        <v>0.02313139391660546</v>
+        <v>0.03162150288555641</v>
       </c>
     </row>
     <row r="136">
@@ -1927,7 +1927,7 @@
         <v>0.3731343283582089</v>
       </c>
       <c r="C136" t="n">
-        <v>0.02296695739543247</v>
+        <v>0.03160913561404943</v>
       </c>
     </row>
     <row r="137">
@@ -1938,7 +1938,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="C137" t="n">
-        <v>0.02277613764752549</v>
+        <v>0.03153708265458832</v>
       </c>
     </row>
     <row r="138">
@@ -1949,7 +1949,7 @@
         <v>0.3676470588235294</v>
       </c>
       <c r="C138" t="n">
-        <v>0.02261096074503104</v>
+        <v>0.03145375558623023</v>
       </c>
     </row>
     <row r="139">
@@ -1960,7 +1960,7 @@
         <v>0.364963503649635</v>
       </c>
       <c r="C139" t="n">
-        <v>0.02252563921993438</v>
+        <v>0.03141265953402455</v>
       </c>
     </row>
     <row r="140">
@@ -1971,7 +1971,7 @@
         <v>0.3623188405797101</v>
       </c>
       <c r="C140" t="n">
-        <v>0.02239483209998509</v>
+        <v>0.03128895112571724</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0.3597122302158273</v>
       </c>
       <c r="C141" t="n">
-        <v>0.02222207499225756</v>
+        <v>0.03108370438151165</v>
       </c>
     </row>
     <row r="142">
@@ -1993,7 +1993,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="C142" t="n">
-        <v>0.02201101209550037</v>
+        <v>0.03084823830182179</v>
       </c>
     </row>
     <row r="143">
@@ -2004,7 +2004,7 @@
         <v>0.3546099290780142</v>
       </c>
       <c r="C143" t="n">
-        <v>0.021766388364925</v>
+        <v>0.03061847763945255</v>
       </c>
     </row>
     <row r="144">
@@ -2015,7 +2015,7 @@
         <v>0.3521126760563381</v>
       </c>
       <c r="C144" t="n">
-        <v>0.02149190866383075</v>
+        <v>0.0304461782573982</v>
       </c>
     </row>
     <row r="145">
@@ -2026,7 +2026,7 @@
         <v>0.3496503496503497</v>
       </c>
       <c r="C145" t="n">
-        <v>0.02119155099373097</v>
+        <v>0.03023903223384018</v>
       </c>
     </row>
     <row r="146">
@@ -2037,7 +2037,7 @@
         <v>0.3472222222222222</v>
       </c>
       <c r="C146" t="n">
-        <v>0.02093292906723415</v>
+        <v>0.02998785509676557</v>
       </c>
     </row>
     <row r="147">
@@ -2048,7 +2048,7 @@
         <v>0.3448275862068966</v>
       </c>
       <c r="C147" t="n">
-        <v>0.0206912883337945</v>
+        <v>0.02969743950882846</v>
       </c>
     </row>
     <row r="148">
@@ -2059,7 +2059,7 @@
         <v>0.3424657534246575</v>
       </c>
       <c r="C148" t="n">
-        <v>0.02050443423201534</v>
+        <v>0.02938879864364871</v>
       </c>
     </row>
     <row r="149">
@@ -2070,7 +2070,7 @@
         <v>0.3401360544217687</v>
       </c>
       <c r="C149" t="n">
-        <v>0.02039046227130056</v>
+        <v>0.0290992332878197</v>
       </c>
     </row>
     <row r="150">
@@ -2081,7 +2081,7 @@
         <v>0.3378378378378378</v>
       </c>
       <c r="C150" t="n">
-        <v>0.02023763188739779</v>
+        <v>0.0288677373090067</v>
       </c>
     </row>
     <row r="151">
@@ -2092,7 +2092,7 @@
         <v>0.3355704697986577</v>
       </c>
       <c r="C151" t="n">
-        <v>0.0200897983662292</v>
+        <v>0.02867845952949623</v>
       </c>
     </row>
     <row r="152">
@@ -2103,7 +2103,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C152" t="n">
-        <v>0.01997165664043023</v>
+        <v>0.02850904378519132</v>
       </c>
     </row>
     <row r="153">
@@ -2114,7 +2114,7 @@
         <v>0.3311258278145696</v>
       </c>
       <c r="C153" t="n">
-        <v>0.0199964275755351</v>
+        <v>0.02832531962758577</v>
       </c>
     </row>
     <row r="154">
@@ -2125,7 +2125,7 @@
         <v>0.3289473684210527</v>
       </c>
       <c r="C154" t="n">
-        <v>0.02001165740605542</v>
+        <v>0.02809349131491031</v>
       </c>
     </row>
     <row r="155">
@@ -2136,7 +2136,7 @@
         <v>0.326797385620915</v>
       </c>
       <c r="C155" t="n">
-        <v>0.01999772283426317</v>
+        <v>0.02784640245879893</v>
       </c>
     </row>
     <row r="156">
@@ -2147,7 +2147,7 @@
         <v>0.3246753246753247</v>
       </c>
       <c r="C156" t="n">
-        <v>0.01998211863318117</v>
+        <v>0.02777299183258938</v>
       </c>
     </row>
     <row r="157">
@@ -2158,7 +2158,7 @@
         <v>0.3225806451612903</v>
       </c>
       <c r="C157" t="n">
-        <v>0.01994485780044623</v>
+        <v>0.02766595648146973</v>
       </c>
     </row>
     <row r="158">
@@ -2169,7 +2169,7 @@
         <v>0.3205128205128205</v>
       </c>
       <c r="C158" t="n">
-        <v>0.02008609860677314</v>
+        <v>0.02772366244038783</v>
       </c>
     </row>
     <row r="159">
@@ -2180,7 +2180,7 @@
         <v>0.3184713375796178</v>
       </c>
       <c r="C159" t="n">
-        <v>0.02022154857827121</v>
+        <v>0.02788044086019873</v>
       </c>
     </row>
     <row r="160">
@@ -2191,7 +2191,7 @@
         <v>0.3164556962025316</v>
       </c>
       <c r="C160" t="n">
-        <v>0.02029019311933923</v>
+        <v>0.02798551123166203</v>
       </c>
     </row>
     <row r="161">
@@ -2202,7 +2202,7 @@
         <v>0.3144654088050314</v>
       </c>
       <c r="C161" t="n">
-        <v>0.02029411147882269</v>
+        <v>0.02807123329783367</v>
       </c>
     </row>
     <row r="162">
@@ -2213,7 +2213,7 @@
         <v>0.3125</v>
       </c>
       <c r="C162" t="n">
-        <v>0.02026675132350964</v>
+        <v>0.02812838886439794</v>
       </c>
     </row>
     <row r="163">
@@ -2224,7 +2224,7 @@
         <v>0.3105590062111801</v>
       </c>
       <c r="C163" t="n">
-        <v>0.02021523283750896</v>
+        <v>0.02812500252699081</v>
       </c>
     </row>
     <row r="164">
@@ -2235,7 +2235,7 @@
         <v>0.308641975308642</v>
       </c>
       <c r="C164" t="n">
-        <v>0.02010833472327761</v>
+        <v>0.02823930594043318</v>
       </c>
     </row>
     <row r="165">
@@ -2246,7 +2246,7 @@
         <v>0.3067484662576687</v>
       </c>
       <c r="C165" t="n">
-        <v>0.02007806638400801</v>
+        <v>0.02851078677876433</v>
       </c>
     </row>
     <row r="166">
@@ -2257,7 +2257,7 @@
         <v>0.3048780487804878</v>
       </c>
       <c r="C166" t="n">
-        <v>0.02001704092757884</v>
+        <v>0.0287386540925949</v>
       </c>
     </row>
     <row r="167">
@@ -2268,7 +2268,7 @@
         <v>0.303030303030303</v>
       </c>
       <c r="C167" t="n">
-        <v>0.01997654383653272</v>
+        <v>0.02891682770856214</v>
       </c>
     </row>
     <row r="168">
@@ -2279,7 +2279,7 @@
         <v>0.3012048192771084</v>
       </c>
       <c r="C168" t="n">
-        <v>0.01990337630138173</v>
+        <v>0.0290439534901749</v>
       </c>
     </row>
     <row r="169">
@@ -2290,7 +2290,7 @@
         <v>0.2994011976047904</v>
       </c>
       <c r="C169" t="n">
-        <v>0.01983662383982587</v>
+        <v>0.02912088149947872</v>
       </c>
     </row>
     <row r="170">
@@ -2301,7 +2301,7 @@
         <v>0.2976190476190476</v>
       </c>
       <c r="C170" t="n">
-        <v>0.01975178942516221</v>
+        <v>0.02914477826973875</v>
       </c>
     </row>
     <row r="171">
@@ -2312,7 +2312,7 @@
         <v>0.2958579881656805</v>
       </c>
       <c r="C171" t="n">
-        <v>0.0196348245353211</v>
+        <v>0.02911732596548544</v>
       </c>
     </row>
     <row r="172">
@@ -2323,7 +2323,7 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="C172" t="n">
-        <v>0.01948734866548988</v>
+        <v>0.02903974451284507</v>
       </c>
     </row>
     <row r="173">
@@ -2334,7 +2334,7 @@
         <v>0.2923976608187134</v>
       </c>
       <c r="C173" t="n">
-        <v>0.01935234024223181</v>
+        <v>0.02900287371576949</v>
       </c>
     </row>
     <row r="174">
@@ -2345,7 +2345,7 @@
         <v>0.2906976744186047</v>
       </c>
       <c r="C174" t="n">
-        <v>0.01931102276550989</v>
+        <v>0.02901206373104787</v>
       </c>
     </row>
     <row r="175">
@@ -2356,7 +2356,7 @@
         <v>0.2890173410404624</v>
       </c>
       <c r="C175" t="n">
-        <v>0.01928453658221288</v>
+        <v>0.02901624817585435</v>
       </c>
     </row>
     <row r="176">
@@ -2367,7 +2367,7 @@
         <v>0.2873563218390804</v>
       </c>
       <c r="C176" t="n">
-        <v>0.0192264016921349</v>
+        <v>0.02896701180372304</v>
       </c>
     </row>
     <row r="177">
@@ -2378,7 +2378,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="C177" t="n">
-        <v>0.01913814798402608</v>
+        <v>0.02893664116188478</v>
       </c>
     </row>
     <row r="178">
@@ -2389,7 +2389,7 @@
         <v>0.2840909090909091</v>
       </c>
       <c r="C178" t="n">
-        <v>0.01902732599647406</v>
+        <v>0.02902657856072038</v>
       </c>
     </row>
     <row r="179">
@@ -2400,7 +2400,7 @@
         <v>0.2824858757062147</v>
       </c>
       <c r="C179" t="n">
-        <v>0.01889606092530108</v>
+        <v>0.02907114114180585</v>
       </c>
     </row>
     <row r="180">
@@ -2411,7 +2411,7 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="C180" t="n">
-        <v>0.01878860792307567</v>
+        <v>0.02918994377476835</v>
       </c>
     </row>
     <row r="181">
@@ -2422,7 +2422,7 @@
         <v>0.2793296089385475</v>
       </c>
       <c r="C181" t="n">
-        <v>0.01865129762225964</v>
+        <v>0.0292679625507705</v>
       </c>
     </row>
     <row r="182">
@@ -2433,7 +2433,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="C182" t="n">
-        <v>0.01848450806705982</v>
+        <v>0.0292983911242131</v>
       </c>
     </row>
     <row r="183">
@@ -2444,7 +2444,7 @@
         <v>0.2762430939226519</v>
       </c>
       <c r="C183" t="n">
-        <v>0.01829078593977986</v>
+        <v>0.02929951920619221</v>
       </c>
     </row>
     <row r="184">
@@ -2455,7 +2455,7 @@
         <v>0.2747252747252747</v>
       </c>
       <c r="C184" t="n">
-        <v>0.01807118541761242</v>
+        <v>0.02925509429377387</v>
       </c>
     </row>
     <row r="185">
@@ -2466,7 +2466,7 @@
         <v>0.273224043715847</v>
       </c>
       <c r="C185" t="n">
-        <v>0.0178273738341801</v>
+        <v>0.02934354172537732</v>
       </c>
     </row>
     <row r="186">
@@ -2477,7 +2477,7 @@
         <v>0.2717391304347826</v>
       </c>
       <c r="C186" t="n">
-        <v>0.01756116515214828</v>
+        <v>0.02940722312462597</v>
       </c>
     </row>
     <row r="187">
@@ -2488,7 +2488,7 @@
         <v>0.2702702702702702</v>
       </c>
       <c r="C187" t="n">
-        <v>0.0173000343909479</v>
+        <v>0.02942219353880432</v>
       </c>
     </row>
     <row r="188">
@@ -2499,7 +2499,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="C188" t="n">
-        <v>0.017034434813095</v>
+        <v>0.02938767218001871</v>
       </c>
     </row>
     <row r="189">
@@ -2510,7 +2510,7 @@
         <v>0.267379679144385</v>
       </c>
       <c r="C189" t="n">
-        <v>0.016771579896958</v>
+        <v>0.02932686848990432</v>
       </c>
     </row>
     <row r="190">
@@ -2521,7 +2521,7 @@
         <v>0.2659574468085106</v>
       </c>
       <c r="C190" t="n">
-        <v>0.01649493312188802</v>
+        <v>0.02922461460666505</v>
       </c>
     </row>
     <row r="191">
@@ -2532,7 +2532,7 @@
         <v>0.2645502645502645</v>
       </c>
       <c r="C191" t="n">
-        <v>0.01623756718319663</v>
+        <v>0.02911994290711162</v>
       </c>
     </row>
     <row r="192">
@@ -2543,7 +2543,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="C192" t="n">
-        <v>0.01603539101006467</v>
+        <v>0.02905496497080505</v>
       </c>
     </row>
     <row r="193">
@@ -2554,7 +2554,7 @@
         <v>0.2617801047120419</v>
       </c>
       <c r="C193" t="n">
-        <v>0.01582604179618566</v>
+        <v>0.02904930430870391</v>
       </c>
     </row>
     <row r="194">
@@ -2565,7 +2565,7 @@
         <v>0.2604166666666667</v>
       </c>
       <c r="C194" t="n">
-        <v>0.0156690547009347</v>
+        <v>0.02904728935011852</v>
       </c>
     </row>
     <row r="195">
@@ -2576,7 +2576,7 @@
         <v>0.2590673575129534</v>
       </c>
       <c r="C195" t="n">
-        <v>0.01552010626933774</v>
+        <v>0.02903761831896307</v>
       </c>
     </row>
     <row r="196">
@@ -2587,7 +2587,7 @@
         <v>0.2577319587628866</v>
       </c>
       <c r="C196" t="n">
-        <v>0.01535522161153422</v>
+        <v>0.02898487377641582</v>
       </c>
     </row>
     <row r="197">
@@ -2598,7 +2598,7 @@
         <v>0.2564102564102564</v>
       </c>
       <c r="C197" t="n">
-        <v>0.01518333468487445</v>
+        <v>0.02889045566579695</v>
       </c>
     </row>
     <row r="198">
@@ -2609,7 +2609,7 @@
         <v>0.2551020408163265</v>
       </c>
       <c r="C198" t="n">
-        <v>0.01500408571600318</v>
+        <v>0.02875533321550184</v>
       </c>
     </row>
     <row r="199">
@@ -2620,7 +2620,7 @@
         <v>0.2538071065989848</v>
       </c>
       <c r="C199" t="n">
-        <v>0.01482319270477853</v>
+        <v>0.02858056401034147</v>
       </c>
     </row>
     <row r="200">
@@ -2631,7 +2631,7 @@
         <v>0.2525252525252525</v>
       </c>
       <c r="C200" t="n">
-        <v>0.01465079843369416</v>
+        <v>0.02836798530766515</v>
       </c>
     </row>
     <row r="201">
@@ -2642,7 +2642,7 @@
         <v>0.2512562814070352</v>
       </c>
       <c r="C201" t="n">
-        <v>0.01448423920447853</v>
+        <v>0.0281172248381231</v>
       </c>
     </row>
     <row r="202">
@@ -2653,7 +2653,7 @@
         <v>0.25</v>
       </c>
       <c r="C202" t="n">
-        <v>0.01432505098895256</v>
+        <v>0.02783073937105768</v>
       </c>
     </row>
   </sheetData>

--- a/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_ver_mean.xlsx
+++ b/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_ver_mean.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3.944278404343558</v>
+        <v>3.257725336414584</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>5.020951023523922</v>
+        <v>4.333776796690947</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>7.675290215436156</v>
+        <v>7.775534583979631</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>16.66666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>11.6596670888235</v>
+        <v>9.629837316317237</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>12.5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.80739756358043</v>
+        <v>9.246621494417738</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>10.4637809880078</v>
+        <v>8.502224744458109</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>7.360057094019317</v>
+        <v>6.255693792685639</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>7.142857142857142</v>
       </c>
       <c r="C9" t="n">
-        <v>5.897360078026272</v>
+        <v>4.14520598949642</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" t="n">
-        <v>6.033852197861362</v>
+        <v>4.379604496825684</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>5.555555555555555</v>
       </c>
       <c r="C11" t="n">
-        <v>4.363397941888826</v>
+        <v>3.280348903180515</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>3.826308280088305</v>
+        <v>2.902149332065886</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>4.545454545454546</v>
       </c>
       <c r="C13" t="n">
-        <v>3.588607811170709</v>
+        <v>2.662621480328188</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>2.871675091408207</v>
+        <v>2.118804152268815</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>3.846153846153846</v>
       </c>
       <c r="C15" t="n">
-        <v>2.502206383384906</v>
+        <v>2.012694889981566</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>3.571428571428571</v>
       </c>
       <c r="C16" t="n">
-        <v>2.498872230571417</v>
+        <v>1.897361414642009</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>2.163546433668063</v>
+        <v>1.659501133853513</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>3.125</v>
       </c>
       <c r="C18" t="n">
-        <v>2.300110800826814</v>
+        <v>1.528096309905365</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>2.941176470588235</v>
       </c>
       <c r="C19" t="n">
-        <v>2.158780549186609</v>
+        <v>1.499679233759038</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="C20" t="n">
-        <v>1.850372169505014</v>
+        <v>1.328878567602191</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="C21" t="n">
-        <v>1.60565589383257</v>
+        <v>1.250863411482662</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>1.392160553910644</v>
+        <v>1.145803105644954</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>2.380952380952381</v>
       </c>
       <c r="C23" t="n">
-        <v>1.251156389097175</v>
+        <v>1.073843793955018</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>2.272727272727273</v>
       </c>
       <c r="C24" t="n">
-        <v>1.172423603775509</v>
+        <v>0.9604482215263361</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>2.173913043478261</v>
       </c>
       <c r="C25" t="n">
-        <v>1.06175636003646</v>
+        <v>0.8512834332902776</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>2.083333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9912713660825129</v>
+        <v>0.7970528157014291</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9101149360215238</v>
+        <v>0.7004747180089087</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>1.923076923076923</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8285789211658626</v>
+        <v>0.6256736414022392</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>1.851851851851852</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7946575053454421</v>
+        <v>0.6218029006131773</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>1.785714285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6996995822866132</v>
+        <v>0.5478348898028386</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>1.724137931034483</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6314833186472916</v>
+        <v>0.4738654088009703</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5763947580127076</v>
+        <v>0.4378736570988899</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1.612903225806452</v>
       </c>
       <c r="C33" t="n">
-        <v>0.567699481684703</v>
+        <v>0.4351982065943187</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1.5625</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5478225508109025</v>
+        <v>0.4202613767485609</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>1.515151515151515</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5123264033926819</v>
+        <v>0.3936426322251615</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>1.470588235294118</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4756575644765453</v>
+        <v>0.3682771251349596</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>1.428571428571428</v>
       </c>
       <c r="C37" t="n">
-        <v>0.45306350026708</v>
+        <v>0.3580445809320706</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>1.388888888888889</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4302738799611929</v>
+        <v>0.354259194715242</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>1.351351351351351</v>
       </c>
       <c r="C39" t="n">
-        <v>0.398076418386218</v>
+        <v>0.3277898659438837</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3736245905664139</v>
+        <v>0.3058401563242633</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>1.282051282051282</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3501797157743412</v>
+        <v>0.2815396717517503</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1.25</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3196253522720414</v>
+        <v>0.2530593518257216</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>1.219512195121951</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2942393848814595</v>
+        <v>0.229393224800498</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>1.19047619047619</v>
       </c>
       <c r="C44" t="n">
-        <v>0.279111903311076</v>
+        <v>0.22223489370746</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1.162790697674419</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2780644049172107</v>
+        <v>0.2279994679352857</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>1.136363636363636</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2783210284396055</v>
+        <v>0.2296073914889947</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2696257073641956</v>
+        <v>0.2228392814049779</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>1.08695652173913</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2549489937252481</v>
+        <v>0.2064600977825861</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>1.063829787234043</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2348044756320157</v>
+        <v>0.1922323415918841</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1.041666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2161347281267111</v>
+        <v>0.1750937561655693</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>1.020408163265306</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2048904111846375</v>
+        <v>0.1633965689865474</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1929719239822753</v>
+        <v>0.1548853700983781</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>0.9803921568627451</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1785047579320738</v>
+        <v>0.1445282251148968</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>0.9615384615384615</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1620877178941875</v>
+        <v>0.1335582257974191</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0.9433962264150942</v>
       </c>
       <c r="C55" t="n">
-        <v>0.148206660281184</v>
+        <v>0.1251609470841034</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0.9259259259259258</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1348378257281491</v>
+        <v>0.1156846987375853</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1292632381765661</v>
+        <v>0.1102977270143657</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0.8928571428571428</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1251533911799537</v>
+        <v>0.1053629880307364</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>0.8771929824561403</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1204902151409818</v>
+        <v>0.09901692975021105</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0.8620689655172414</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1161231457398282</v>
+        <v>0.09467709959818747</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0.8474576271186441</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1118659910646052</v>
+        <v>0.0904937673672165</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C62" t="n">
-        <v>0.1079232139516871</v>
+        <v>0.08793969757019296</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0.819672131147541</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1043574688553683</v>
+        <v>0.08687312909878855</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0.8064516129032259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1005989201783777</v>
+        <v>0.08635742812975282</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0.7936507936507936</v>
       </c>
       <c r="C65" t="n">
-        <v>0.09675746369736624</v>
+        <v>0.08595541335334085</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0.78125</v>
       </c>
       <c r="C66" t="n">
-        <v>0.09301195429596422</v>
+        <v>0.08519750611921062</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>0.7692307692307692</v>
       </c>
       <c r="C67" t="n">
-        <v>0.08983466812940215</v>
+        <v>0.08519950003814507</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0.7575757575757576</v>
       </c>
       <c r="C68" t="n">
-        <v>0.08679284950670739</v>
+        <v>0.0851394552474052</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0.7462686567164178</v>
       </c>
       <c r="C69" t="n">
-        <v>0.08393245526599982</v>
+        <v>0.08375055120638146</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0.7352941176470588</v>
       </c>
       <c r="C70" t="n">
-        <v>0.08127204471765409</v>
+        <v>0.08164998323925658</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0.7246376811594202</v>
       </c>
       <c r="C71" t="n">
-        <v>0.07947015951263267</v>
+        <v>0.07957723442989786</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07802326366899159</v>
+        <v>0.0769434218591253</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0.7042253521126761</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0764377435430679</v>
+        <v>0.07362885032057975</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C74" t="n">
-        <v>0.07457803453663694</v>
+        <v>0.07133804995489633</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>0.684931506849315</v>
       </c>
       <c r="C75" t="n">
-        <v>0.07249504644142653</v>
+        <v>0.06830851524494375</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0.6756756756756757</v>
       </c>
       <c r="C76" t="n">
-        <v>0.07100258457344531</v>
+        <v>0.06539197367650654</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C77" t="n">
-        <v>0.06954661807104259</v>
+        <v>0.06232997862263442</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="C78" t="n">
-        <v>0.06840896459535262</v>
+        <v>0.0598175170881186</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0.6493506493506493</v>
       </c>
       <c r="C79" t="n">
-        <v>0.06750518342048371</v>
+        <v>0.05936092221377195</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0.641025641025641</v>
       </c>
       <c r="C80" t="n">
-        <v>0.06653145042423626</v>
+        <v>0.05868679931968711</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0.6329113924050632</v>
       </c>
       <c r="C81" t="n">
-        <v>0.065476223792761</v>
+        <v>0.0577574016995361</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         <v>0.625</v>
       </c>
       <c r="C82" t="n">
-        <v>0.06447355159940323</v>
+        <v>0.05666883616179979</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0.6172839506172839</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0630910293164991</v>
+        <v>0.05549386069954386</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0.6097560975609756</v>
       </c>
       <c r="C84" t="n">
-        <v>0.06187639648545896</v>
+        <v>0.05442225402436317</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0.6024096385542168</v>
       </c>
       <c r="C85" t="n">
-        <v>0.06087972863756826</v>
+        <v>0.05364320220684404</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0.5952380952380952</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0597493171955976</v>
+        <v>0.05281867904761301</v>
       </c>
     </row>
     <row r="87">
@@ -1388,7 +1388,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="C87" t="n">
-        <v>0.05909432295496605</v>
+        <v>0.05191281216208919</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0.5813953488372093</v>
       </c>
       <c r="C88" t="n">
-        <v>0.05820982549005007</v>
+        <v>0.05096347768463434</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0.5747126436781609</v>
       </c>
       <c r="C89" t="n">
-        <v>0.05707246599837611</v>
+        <v>0.05037593306986533</v>
       </c>
     </row>
     <row r="90">
@@ -1421,7 +1421,7 @@
         <v>0.5681818181818182</v>
       </c>
       <c r="C90" t="n">
-        <v>0.05571568702921632</v>
+        <v>0.04963863580275805</v>
       </c>
     </row>
     <row r="91">
@@ -1432,7 +1432,7 @@
         <v>0.5617977528089888</v>
       </c>
       <c r="C91" t="n">
-        <v>0.05417609992965031</v>
+        <v>0.04872672880105441</v>
       </c>
     </row>
     <row r="92">
@@ -1443,7 +1443,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C92" t="n">
-        <v>0.05249803841995235</v>
+        <v>0.04760182585152947</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0.5494505494505494</v>
       </c>
       <c r="C93" t="n">
-        <v>0.05081127175902615</v>
+        <v>0.04632010887223694</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
         <v>0.5434782608695652</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0496359938103669</v>
+        <v>0.0453682245910501</v>
       </c>
     </row>
     <row r="95">
@@ -1476,7 +1476,7 @@
         <v>0.5376344086021505</v>
       </c>
       <c r="C95" t="n">
-        <v>0.04843081148454349</v>
+        <v>0.04437455712236311</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0.5319148936170213</v>
       </c>
       <c r="C96" t="n">
-        <v>0.04720048088038863</v>
+        <v>0.04329691314402276</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="C97" t="n">
-        <v>0.04592626185523781</v>
+        <v>0.04295308657095803</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="C98" t="n">
-        <v>0.04462470652280688</v>
+        <v>0.04278041733350447</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0.5154639175257733</v>
       </c>
       <c r="C99" t="n">
-        <v>0.04331123454096408</v>
+        <v>0.04248485355118495</v>
       </c>
     </row>
     <row r="100">
@@ -1531,7 +1531,7 @@
         <v>0.5102040816326531</v>
       </c>
       <c r="C100" t="n">
-        <v>0.04199726613491252</v>
+        <v>0.04204834091460481</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0.5050505050505051</v>
       </c>
       <c r="C101" t="n">
-        <v>0.04069356421414314</v>
+        <v>0.04146127156568622</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="C102" t="n">
-        <v>0.03940916274217949</v>
+        <v>0.04072168003451009</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0.495049504950495</v>
       </c>
       <c r="C103" t="n">
-        <v>0.03815151151213785</v>
+        <v>0.03984349086380241</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0.4901960784313725</v>
       </c>
       <c r="C104" t="n">
-        <v>0.03727339924948441</v>
+        <v>0.03918028695322383</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0.4854368932038835</v>
       </c>
       <c r="C105" t="n">
-        <v>0.03640310394040151</v>
+        <v>0.03836955953260526</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0.4807692307692307</v>
       </c>
       <c r="C106" t="n">
-        <v>0.03553713017608547</v>
+        <v>0.03742615712650233</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="C107" t="n">
-        <v>0.03467806240170505</v>
+        <v>0.03637495198409297</v>
       </c>
     </row>
     <row r="108">
@@ -1619,7 +1619,7 @@
         <v>0.4716981132075471</v>
       </c>
       <c r="C108" t="n">
-        <v>0.03408677395618948</v>
+        <v>0.03526765708776768</v>
       </c>
     </row>
     <row r="109">
@@ -1630,7 +1630,7 @@
         <v>0.4672897196261682</v>
       </c>
       <c r="C109" t="n">
-        <v>0.03373498123082606</v>
+        <v>0.03411460796031124</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0.4629629629629629</v>
       </c>
       <c r="C110" t="n">
-        <v>0.03333502712933775</v>
+        <v>0.032944747919026</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0.4587155963302752</v>
       </c>
       <c r="C111" t="n">
-        <v>0.03310867471878388</v>
+        <v>0.03200832876094005</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="C112" t="n">
-        <v>0.03278221192053979</v>
+        <v>0.03105055545846217</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0.4504504504504504</v>
       </c>
       <c r="C113" t="n">
-        <v>0.03241168819511638</v>
+        <v>0.03013946167466795</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0.4464285714285714</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0319845571163179</v>
+        <v>0.02926798760592771</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0.4424778761061947</v>
       </c>
       <c r="C115" t="n">
-        <v>0.03156369919206451</v>
+        <v>0.0287920732039761</v>
       </c>
     </row>
     <row r="116">
@@ -1707,7 +1707,7 @@
         <v>0.4385964912280702</v>
       </c>
       <c r="C116" t="n">
-        <v>0.031230907827427</v>
+        <v>0.02853190531614525</v>
       </c>
     </row>
     <row r="117">
@@ -1718,7 +1718,7 @@
         <v>0.4347826086956521</v>
       </c>
       <c r="C117" t="n">
-        <v>0.03086455651118517</v>
+        <v>0.02820138269264248</v>
       </c>
     </row>
     <row r="118">
@@ -1729,7 +1729,7 @@
         <v>0.4310344827586207</v>
       </c>
       <c r="C118" t="n">
-        <v>0.03048290422484105</v>
+        <v>0.02781436869425227</v>
       </c>
     </row>
     <row r="119">
@@ -1740,7 +1740,7 @@
         <v>0.4273504273504274</v>
       </c>
       <c r="C119" t="n">
-        <v>0.03039004282314444</v>
+        <v>0.02758005677177168</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0.4237288135593221</v>
       </c>
       <c r="C120" t="n">
-        <v>0.03038764103076888</v>
+        <v>0.02732089798892236</v>
       </c>
     </row>
     <row r="121">
@@ -1762,7 +1762,7 @@
         <v>0.4201680672268908</v>
       </c>
       <c r="C121" t="n">
-        <v>0.03035605321489763</v>
+        <v>0.02703528735664602</v>
       </c>
     </row>
     <row r="122">
@@ -1773,7 +1773,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="C122" t="n">
-        <v>0.0302946046547351</v>
+        <v>0.02673100962448337</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0.4132231404958678</v>
       </c>
       <c r="C123" t="n">
-        <v>0.03020101516944925</v>
+        <v>0.02648998198360383</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0.4098360655737705</v>
       </c>
       <c r="C124" t="n">
-        <v>0.030072677403433</v>
+        <v>0.02624504280355892</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0.4065040650406504</v>
       </c>
       <c r="C125" t="n">
-        <v>0.02991623019302811</v>
+        <v>0.02610170076253928</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0.4032258064516129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.02995155419958708</v>
+        <v>0.02627521644849455</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0.4</v>
       </c>
       <c r="C127" t="n">
-        <v>0.03016375204733994</v>
+        <v>0.02642119958949407</v>
       </c>
     </row>
     <row r="128">
@@ -1839,7 +1839,7 @@
         <v>0.3968253968253968</v>
       </c>
       <c r="C128" t="n">
-        <v>0.03040065051785558</v>
+        <v>0.02656700269375996</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0.3937007874015748</v>
       </c>
       <c r="C129" t="n">
-        <v>0.03066743469714051</v>
+        <v>0.02672104637235547</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0.390625</v>
       </c>
       <c r="C130" t="n">
-        <v>0.03092140856179061</v>
+        <v>0.02684567584991845</v>
       </c>
     </row>
     <row r="131">
@@ -1872,7 +1872,7 @@
         <v>0.3875968992248062</v>
       </c>
       <c r="C131" t="n">
-        <v>0.03114599099367791</v>
+        <v>0.02693066921290891</v>
       </c>
     </row>
     <row r="132">
@@ -1883,7 +1883,7 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="C132" t="n">
-        <v>0.03133151695580981</v>
+        <v>0.02697352755452306</v>
       </c>
     </row>
     <row r="133">
@@ -1894,7 +1894,7 @@
         <v>0.3816793893129771</v>
       </c>
       <c r="C133" t="n">
-        <v>0.03146909574005762</v>
+        <v>0.02697283136392679</v>
       </c>
     </row>
     <row r="134">
@@ -1905,7 +1905,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>0.03157053424799306</v>
+        <v>0.02694461414662506</v>
       </c>
     </row>
     <row r="135">
@@ -1916,7 +1916,7 @@
         <v>0.3759398496240601</v>
       </c>
       <c r="C135" t="n">
-        <v>0.03162150288555641</v>
+        <v>0.02688384942873377</v>
       </c>
     </row>
     <row r="136">
@@ -1927,7 +1927,7 @@
         <v>0.3731343283582089</v>
       </c>
       <c r="C136" t="n">
-        <v>0.03160913561404943</v>
+        <v>0.02678377560128531</v>
       </c>
     </row>
     <row r="137">
@@ -1938,7 +1938,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="C137" t="n">
-        <v>0.03153708265458832</v>
+        <v>0.02665284549560372</v>
       </c>
     </row>
     <row r="138">
@@ -1949,7 +1949,7 @@
         <v>0.3676470588235294</v>
       </c>
       <c r="C138" t="n">
-        <v>0.03145375558623023</v>
+        <v>0.0265429744457933</v>
       </c>
     </row>
     <row r="139">
@@ -1960,7 +1960,7 @@
         <v>0.364963503649635</v>
       </c>
       <c r="C139" t="n">
-        <v>0.03141265953402455</v>
+        <v>0.02650829719158489</v>
       </c>
     </row>
     <row r="140">
@@ -1971,7 +1971,7 @@
         <v>0.3623188405797101</v>
       </c>
       <c r="C140" t="n">
-        <v>0.03128895112571724</v>
+        <v>0.02642342510992816</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0.3597122302158273</v>
       </c>
       <c r="C141" t="n">
-        <v>0.03108370438151165</v>
+        <v>0.02629187196559281</v>
       </c>
     </row>
     <row r="142">
@@ -1993,7 +1993,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="C142" t="n">
-        <v>0.03084823830182179</v>
+        <v>0.02611728066564173</v>
       </c>
     </row>
     <row r="143">
@@ -2004,7 +2004,7 @@
         <v>0.3546099290780142</v>
       </c>
       <c r="C143" t="n">
-        <v>0.03061847763945255</v>
+        <v>0.02590440976839615</v>
       </c>
     </row>
     <row r="144">
@@ -2015,7 +2015,7 @@
         <v>0.3521126760563381</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0304461782573982</v>
+        <v>0.02565698701950454</v>
       </c>
     </row>
     <row r="145">
@@ -2026,7 +2026,7 @@
         <v>0.3496503496503497</v>
       </c>
       <c r="C145" t="n">
-        <v>0.03023903223384018</v>
+        <v>0.02537901735522518</v>
       </c>
     </row>
     <row r="146">
@@ -2037,7 +2037,7 @@
         <v>0.3472222222222222</v>
       </c>
       <c r="C146" t="n">
-        <v>0.02998785509676557</v>
+        <v>0.02513777175084154</v>
       </c>
     </row>
     <row r="147">
@@ -2048,7 +2048,7 @@
         <v>0.3448275862068966</v>
       </c>
       <c r="C147" t="n">
-        <v>0.02969743950882846</v>
+        <v>0.02490782311910187</v>
       </c>
     </row>
     <row r="148">
@@ -2059,7 +2059,7 @@
         <v>0.3424657534246575</v>
       </c>
       <c r="C148" t="n">
-        <v>0.02938879864364871</v>
+        <v>0.02463909610420223</v>
       </c>
     </row>
     <row r="149">
@@ -2070,7 +2070,7 @@
         <v>0.3401360544217687</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0290992332878197</v>
+        <v>0.02433614593339631</v>
       </c>
     </row>
     <row r="150">
@@ -2081,7 +2081,7 @@
         <v>0.3378378378378378</v>
       </c>
       <c r="C150" t="n">
-        <v>0.0288677373090067</v>
+        <v>0.02403964601860972</v>
       </c>
     </row>
     <row r="151">
@@ -2092,7 +2092,7 @@
         <v>0.3355704697986577</v>
       </c>
       <c r="C151" t="n">
-        <v>0.02867845952949623</v>
+        <v>0.02380473967346744</v>
       </c>
     </row>
     <row r="152">
@@ -2103,7 +2103,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C152" t="n">
-        <v>0.02850904378519132</v>
+        <v>0.02361602998641812</v>
       </c>
     </row>
     <row r="153">
@@ -2114,7 +2114,7 @@
         <v>0.3311258278145696</v>
       </c>
       <c r="C153" t="n">
-        <v>0.02832531962758577</v>
+        <v>0.02349256124639286</v>
       </c>
     </row>
     <row r="154">
@@ -2125,7 +2125,7 @@
         <v>0.3289473684210527</v>
       </c>
       <c r="C154" t="n">
-        <v>0.02809349131491031</v>
+        <v>0.02335211694609092</v>
       </c>
     </row>
     <row r="155">
@@ -2136,7 +2136,7 @@
         <v>0.326797385620915</v>
       </c>
       <c r="C155" t="n">
-        <v>0.02784640245879893</v>
+        <v>0.02320765057021774</v>
       </c>
     </row>
     <row r="156">
@@ -2147,7 +2147,7 @@
         <v>0.3246753246753247</v>
       </c>
       <c r="C156" t="n">
-        <v>0.02777299183258938</v>
+        <v>0.0232447985929842</v>
       </c>
     </row>
     <row r="157">
@@ -2158,7 +2158,7 @@
         <v>0.3225806451612903</v>
       </c>
       <c r="C157" t="n">
-        <v>0.02766595648146973</v>
+        <v>0.02325369189175141</v>
       </c>
     </row>
     <row r="158">
@@ -2169,7 +2169,7 @@
         <v>0.3205128205128205</v>
       </c>
       <c r="C158" t="n">
-        <v>0.02772366244038783</v>
+        <v>0.02343427267789741</v>
       </c>
     </row>
     <row r="159">
@@ -2180,7 +2180,7 @@
         <v>0.3184713375796178</v>
       </c>
       <c r="C159" t="n">
-        <v>0.02788044086019873</v>
+        <v>0.02360144151836771</v>
       </c>
     </row>
     <row r="160">
@@ -2191,7 +2191,7 @@
         <v>0.3164556962025316</v>
       </c>
       <c r="C160" t="n">
-        <v>0.02798551123166203</v>
+        <v>0.02369428369937472</v>
       </c>
     </row>
     <row r="161">
@@ -2202,7 +2202,7 @@
         <v>0.3144654088050314</v>
       </c>
       <c r="C161" t="n">
-        <v>0.02807123329783367</v>
+        <v>0.02375406731396561</v>
       </c>
     </row>
     <row r="162">
@@ -2213,7 +2213,7 @@
         <v>0.3125</v>
       </c>
       <c r="C162" t="n">
-        <v>0.02812838886439794</v>
+        <v>0.02377234673633661</v>
       </c>
     </row>
     <row r="163">
@@ -2224,7 +2224,7 @@
         <v>0.3105590062111801</v>
       </c>
       <c r="C163" t="n">
-        <v>0.02812500252699081</v>
+        <v>0.02371801519836325</v>
       </c>
     </row>
     <row r="164">
@@ -2235,7 +2235,7 @@
         <v>0.308641975308642</v>
       </c>
       <c r="C164" t="n">
-        <v>0.02823930594043318</v>
+        <v>0.02377025634106439</v>
       </c>
     </row>
     <row r="165">
@@ -2246,7 +2246,7 @@
         <v>0.3067484662576687</v>
       </c>
       <c r="C165" t="n">
-        <v>0.02851078677876433</v>
+        <v>0.02396958360139105</v>
       </c>
     </row>
     <row r="166">
@@ -2257,7 +2257,7 @@
         <v>0.3048780487804878</v>
       </c>
       <c r="C166" t="n">
-        <v>0.0287386540925949</v>
+        <v>0.02411629837266904</v>
       </c>
     </row>
     <row r="167">
@@ -2268,7 +2268,7 @@
         <v>0.303030303030303</v>
       </c>
       <c r="C167" t="n">
-        <v>0.02891682770856214</v>
+        <v>0.02420547383152709</v>
       </c>
     </row>
     <row r="168">
@@ -2279,7 +2279,7 @@
         <v>0.3012048192771084</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0290439534901749</v>
+        <v>0.02423717882021405</v>
       </c>
     </row>
     <row r="169">
@@ -2290,7 +2290,7 @@
         <v>0.2994011976047904</v>
       </c>
       <c r="C169" t="n">
-        <v>0.02912088149947872</v>
+        <v>0.02421359523563335</v>
       </c>
     </row>
     <row r="170">
@@ -2301,7 +2301,7 @@
         <v>0.2976190476190476</v>
       </c>
       <c r="C170" t="n">
-        <v>0.02914477826973875</v>
+        <v>0.02413295970805808</v>
       </c>
     </row>
     <row r="171">
@@ -2312,7 +2312,7 @@
         <v>0.2958579881656805</v>
       </c>
       <c r="C171" t="n">
-        <v>0.02911732596548544</v>
+        <v>0.0239983051273583</v>
       </c>
     </row>
     <row r="172">
@@ -2323,7 +2323,7 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="C172" t="n">
-        <v>0.02903974451284507</v>
+        <v>0.02381223701804618</v>
       </c>
     </row>
     <row r="173">
@@ -2334,7 +2334,7 @@
         <v>0.2923976608187134</v>
       </c>
       <c r="C173" t="n">
-        <v>0.02900287371576949</v>
+        <v>0.02366700871135703</v>
       </c>
     </row>
     <row r="174">
@@ -2345,7 +2345,7 @@
         <v>0.2906976744186047</v>
       </c>
       <c r="C174" t="n">
-        <v>0.02901206373104787</v>
+        <v>0.02356940374216012</v>
       </c>
     </row>
     <row r="175">
@@ -2356,7 +2356,7 @@
         <v>0.2890173410404624</v>
       </c>
       <c r="C175" t="n">
-        <v>0.02901624817585435</v>
+        <v>0.02346979974488341</v>
       </c>
     </row>
     <row r="176">
@@ -2367,7 +2367,7 @@
         <v>0.2873563218390804</v>
       </c>
       <c r="C176" t="n">
-        <v>0.02896701180372304</v>
+        <v>0.02332122586136137</v>
       </c>
     </row>
     <row r="177">
@@ -2378,7 +2378,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="C177" t="n">
-        <v>0.02893664116188478</v>
+        <v>0.02319738181892336</v>
       </c>
     </row>
     <row r="178">
@@ -2389,7 +2389,7 @@
         <v>0.2840909090909091</v>
       </c>
       <c r="C178" t="n">
-        <v>0.02902657856072038</v>
+        <v>0.02320899193046438</v>
       </c>
     </row>
     <row r="179">
@@ -2400,7 +2400,7 @@
         <v>0.2824858757062147</v>
       </c>
       <c r="C179" t="n">
-        <v>0.02907114114180585</v>
+        <v>0.02318378112267188</v>
       </c>
     </row>
     <row r="180">
@@ -2411,7 +2411,7 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="C180" t="n">
-        <v>0.02918994377476835</v>
+        <v>0.02324262694489326</v>
       </c>
     </row>
     <row r="181">
@@ -2422,7 +2422,7 @@
         <v>0.2793296089385475</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0292679625507705</v>
+        <v>0.02327171060717691</v>
       </c>
     </row>
     <row r="182">
@@ -2433,7 +2433,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="C182" t="n">
-        <v>0.0292983911242131</v>
+        <v>0.02326536239866496</v>
       </c>
     </row>
     <row r="183">
@@ -2444,7 +2444,7 @@
         <v>0.2762430939226519</v>
       </c>
       <c r="C183" t="n">
-        <v>0.02929951920619221</v>
+        <v>0.02324292955330036</v>
       </c>
     </row>
     <row r="184">
@@ -2455,7 +2455,7 @@
         <v>0.2747252747252747</v>
       </c>
       <c r="C184" t="n">
-        <v>0.02925509429377387</v>
+        <v>0.0231891278685453</v>
       </c>
     </row>
     <row r="185">
@@ -2466,7 +2466,7 @@
         <v>0.273224043715847</v>
       </c>
       <c r="C185" t="n">
-        <v>0.02934354172537732</v>
+        <v>0.02309662328199154</v>
       </c>
     </row>
     <row r="186">
@@ -2477,7 +2477,7 @@
         <v>0.2717391304347826</v>
       </c>
       <c r="C186" t="n">
-        <v>0.02940722312462597</v>
+        <v>0.0229694763554746</v>
       </c>
     </row>
     <row r="187">
@@ -2488,7 +2488,7 @@
         <v>0.2702702702702702</v>
       </c>
       <c r="C187" t="n">
-        <v>0.02942219353880432</v>
+        <v>0.02280763961875705</v>
       </c>
     </row>
     <row r="188">
@@ -2499,7 +2499,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="C188" t="n">
-        <v>0.02938767218001871</v>
+        <v>0.02261201081590363</v>
       </c>
     </row>
     <row r="189">
@@ -2510,7 +2510,7 @@
         <v>0.267379679144385</v>
       </c>
       <c r="C189" t="n">
-        <v>0.02932686848990432</v>
+        <v>0.02240702130914101</v>
       </c>
     </row>
     <row r="190">
@@ -2521,7 +2521,7 @@
         <v>0.2659574468085106</v>
       </c>
       <c r="C190" t="n">
-        <v>0.02922461460666505</v>
+        <v>0.02217673196277619</v>
       </c>
     </row>
     <row r="191">
@@ -2532,7 +2532,7 @@
         <v>0.2645502645502645</v>
       </c>
       <c r="C191" t="n">
-        <v>0.02911994290711162</v>
+        <v>0.02196383470050208</v>
       </c>
     </row>
     <row r="192">
@@ -2543,7 +2543,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="C192" t="n">
-        <v>0.02905496497080505</v>
+        <v>0.02181198915373342</v>
       </c>
     </row>
     <row r="193">
@@ -2554,7 +2554,7 @@
         <v>0.2617801047120419</v>
       </c>
       <c r="C193" t="n">
-        <v>0.02904930430870391</v>
+        <v>0.02163509473553273</v>
       </c>
     </row>
     <row r="194">
@@ -2565,7 +2565,7 @@
         <v>0.2604166666666667</v>
       </c>
       <c r="C194" t="n">
-        <v>0.02904728935011852</v>
+        <v>0.02143475629018325</v>
       </c>
     </row>
     <row r="195">
@@ -2576,7 +2576,7 @@
         <v>0.2590673575129534</v>
       </c>
       <c r="C195" t="n">
-        <v>0.02903761831896307</v>
+        <v>0.02124914557589814</v>
       </c>
     </row>
     <row r="196">
@@ -2587,7 +2587,7 @@
         <v>0.2577319587628866</v>
       </c>
       <c r="C196" t="n">
-        <v>0.02898487377641582</v>
+        <v>0.02104391222080781</v>
       </c>
     </row>
     <row r="197">
@@ -2598,7 +2598,7 @@
         <v>0.2564102564102564</v>
       </c>
       <c r="C197" t="n">
-        <v>0.02889045566579695</v>
+        <v>0.02082131406371187</v>
       </c>
     </row>
     <row r="198">
@@ -2609,7 +2609,7 @@
         <v>0.2551020408163265</v>
       </c>
       <c r="C198" t="n">
-        <v>0.02875533321550184</v>
+        <v>0.0205829683665515</v>
       </c>
     </row>
     <row r="199">
@@ -2620,7 +2620,7 @@
         <v>0.2538071065989848</v>
       </c>
       <c r="C199" t="n">
-        <v>0.02858056401034147</v>
+        <v>0.020329352668713</v>
       </c>
     </row>
     <row r="200">
@@ -2631,7 +2631,7 @@
         <v>0.2525252525252525</v>
       </c>
       <c r="C200" t="n">
-        <v>0.02836798530766515</v>
+        <v>0.02006188140554565</v>
       </c>
     </row>
     <row r="201">
@@ -2642,7 +2642,7 @@
         <v>0.2512562814070352</v>
       </c>
       <c r="C201" t="n">
-        <v>0.0281172248381231</v>
+        <v>0.01978749832109078</v>
       </c>
     </row>
     <row r="202">
@@ -2653,7 +2653,7 @@
         <v>0.25</v>
       </c>
       <c r="C202" t="n">
-        <v>0.02783073937105768</v>
+        <v>0.01951190270252014</v>
       </c>
     </row>
   </sheetData>

--- a/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_ver_mean.xlsx
+++ b/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_ver_mean.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3.257725336414584</v>
+        <v>3.815654653518844</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>4.333776796690947</v>
+        <v>5.153710003390449</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>7.775534583979631</v>
+        <v>7.354206047676862</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>16.66666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>9.629837316317237</v>
+        <v>12.48926100130826</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>12.5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.246621494417738</v>
+        <v>15.83302562317605</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>8.502224744458109</v>
+        <v>10.25141741909504</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>6.255693792685639</v>
+        <v>7.042555545154105</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>7.142857142857142</v>
       </c>
       <c r="C9" t="n">
-        <v>4.14520598949642</v>
+        <v>5.688280728361669</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" t="n">
-        <v>4.379604496825684</v>
+        <v>5.94145865157012</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>5.555555555555555</v>
       </c>
       <c r="C11" t="n">
-        <v>3.280348903180515</v>
+        <v>4.188161444125927</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>2.902149332065886</v>
+        <v>3.521183005091223</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>4.545454545454546</v>
       </c>
       <c r="C13" t="n">
-        <v>2.662621480328188</v>
+        <v>3.48916835674375</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>2.118804152268815</v>
+        <v>2.897215942840648</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>3.846153846153846</v>
       </c>
       <c r="C15" t="n">
-        <v>2.012694889981566</v>
+        <v>2.432642496084197</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>3.571428571428571</v>
       </c>
       <c r="C16" t="n">
-        <v>1.897361414642009</v>
+        <v>2.476968994235145</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>1.659501133853513</v>
+        <v>2.107215881666337</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>3.125</v>
       </c>
       <c r="C18" t="n">
-        <v>1.528096309905365</v>
+        <v>2.283528315440766</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>2.941176470588235</v>
       </c>
       <c r="C19" t="n">
-        <v>1.499679233759038</v>
+        <v>2.131239914393078</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="C20" t="n">
-        <v>1.328878567602191</v>
+        <v>1.752506555908268</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="C21" t="n">
-        <v>1.250863411482662</v>
+        <v>1.514968268087701</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>1.145803105644954</v>
+        <v>1.336523358847249</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>2.380952380952381</v>
       </c>
       <c r="C23" t="n">
-        <v>1.073843793955018</v>
+        <v>1.169814362660892</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>2.272727272727273</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9604482215263361</v>
+        <v>1.105113858342941</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>2.173913043478261</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8512834332902776</v>
+        <v>1.013142932027836</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>2.083333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7970528157014291</v>
+        <v>0.9453571459212116</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7004747180089087</v>
+        <v>0.8890810706859564</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>1.923076923076923</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6256736414022392</v>
+        <v>0.8192242980517966</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>1.851851851851852</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6218029006131773</v>
+        <v>0.7826765159119705</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>1.785714285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5478348898028386</v>
+        <v>0.6716823459464167</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>1.724137931034483</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4738654088009703</v>
+        <v>0.6220055614009956</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4378736570988899</v>
+        <v>0.5735066635638121</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1.612903225806452</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4351982065943187</v>
+        <v>0.563487111819186</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1.5625</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4202613767485609</v>
+        <v>0.5445180921962028</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>1.515151515151515</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3936426322251615</v>
+        <v>0.5134291397854217</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>1.470588235294118</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3682771251349596</v>
+        <v>0.4780068390555436</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>1.428571428571428</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3580445809320706</v>
+        <v>0.4510783714238037</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>1.388888888888889</v>
       </c>
       <c r="C38" t="n">
-        <v>0.354259194715242</v>
+        <v>0.4262434831829797</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>1.351351351351351</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3277898659438837</v>
+        <v>0.392450887647556</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3058401563242633</v>
+        <v>0.3676960375618032</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>1.282051282051282</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2815396717517503</v>
+        <v>0.3410461391966033</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1.25</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2530593518257216</v>
+        <v>0.3136972236453328</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>1.219512195121951</v>
       </c>
       <c r="C43" t="n">
-        <v>0.229393224800498</v>
+        <v>0.2906167815141337</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>1.19047619047619</v>
       </c>
       <c r="C44" t="n">
-        <v>0.22223489370746</v>
+        <v>0.2752155048822763</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1.162790697674419</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2279994679352857</v>
+        <v>0.2751043010613121</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>1.136363636363636</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2296073914889947</v>
+        <v>0.2766798480275103</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2228392814049779</v>
+        <v>0.2683579025441594</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>1.08695652173913</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2064600977825861</v>
+        <v>0.2538928793458166</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>1.063829787234043</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1922323415918841</v>
+        <v>0.2336879252063725</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1.041666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1750937561655693</v>
+        <v>0.2139764301477924</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>1.020408163265306</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1633965689865474</v>
+        <v>0.2021024231208301</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1548853700983781</v>
+        <v>0.1893130219324765</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>0.9803921568627451</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1445282251148968</v>
+        <v>0.1740161292942842</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>0.9615384615384615</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1335582257974191</v>
+        <v>0.1575551664674015</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0.9433962264150942</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1251609470841034</v>
+        <v>0.1452264051561916</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0.9259259259259258</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1156846987375853</v>
+        <v>0.1341275453422243</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1102977270143657</v>
+        <v>0.1292094702812406</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0.8928571428571428</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1053629880307364</v>
+        <v>0.1249049342430107</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>0.8771929824561403</v>
       </c>
       <c r="C59" t="n">
-        <v>0.09901692975021105</v>
+        <v>0.1200108904653176</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0.8620689655172414</v>
       </c>
       <c r="C60" t="n">
-        <v>0.09467709959818747</v>
+        <v>0.1156091166299663</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0.8474576271186441</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0904937673672165</v>
+        <v>0.1122929710945865</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C62" t="n">
-        <v>0.08793969757019296</v>
+        <v>0.1090645455115595</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0.819672131147541</v>
       </c>
       <c r="C63" t="n">
-        <v>0.08687312909878855</v>
+        <v>0.1054026783867385</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0.8064516129032259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.08635742812975282</v>
+        <v>0.1015033266084783</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0.7936507936507936</v>
       </c>
       <c r="C65" t="n">
-        <v>0.08595541335334085</v>
+        <v>0.09759726421372661</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0.78125</v>
       </c>
       <c r="C66" t="n">
-        <v>0.08519750611921062</v>
+        <v>0.09387566397117691</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>0.7692307692307692</v>
       </c>
       <c r="C67" t="n">
-        <v>0.08519950003814507</v>
+        <v>0.09047135255285368</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0.7575757575757576</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0851394552474052</v>
+        <v>0.08745383170113263</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0.7462686567164178</v>
       </c>
       <c r="C69" t="n">
-        <v>0.08375055120638146</v>
+        <v>0.08483567102685127</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0.7352941176470588</v>
       </c>
       <c r="C70" t="n">
-        <v>0.08164998323925658</v>
+        <v>0.08259283658622459</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0.7246376811594202</v>
       </c>
       <c r="C71" t="n">
-        <v>0.07957723442989786</v>
+        <v>0.08125408958010853</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0769434218591253</v>
+        <v>0.0800408585747055</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0.7042253521126761</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07362885032057975</v>
+        <v>0.078765675056821</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C74" t="n">
-        <v>0.07133804995489633</v>
+        <v>0.07724926508674694</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>0.684931506849315</v>
       </c>
       <c r="C75" t="n">
-        <v>0.06830851524494375</v>
+        <v>0.0754974161445932</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0.6756756756756757</v>
       </c>
       <c r="C76" t="n">
-        <v>0.06539197367650654</v>
+        <v>0.07429793434657607</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C77" t="n">
-        <v>0.06232997862263442</v>
+        <v>0.0730451425075186</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0598175170881186</v>
+        <v>0.07192118421652334</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0.6493506493506493</v>
       </c>
       <c r="C79" t="n">
-        <v>0.05936092221377195</v>
+        <v>0.07098048953736903</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0.641025641025641</v>
       </c>
       <c r="C80" t="n">
-        <v>0.05868679931968711</v>
+        <v>0.06991254815731297</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0.6329113924050632</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0577574016995361</v>
+        <v>0.06871445101172245</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         <v>0.625</v>
       </c>
       <c r="C82" t="n">
-        <v>0.05666883616179979</v>
+        <v>0.06750817229209233</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0.6172839506172839</v>
       </c>
       <c r="C83" t="n">
-        <v>0.05549386069954386</v>
+        <v>0.06587531406756048</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0.6097560975609756</v>
       </c>
       <c r="C84" t="n">
-        <v>0.05442225402436317</v>
+        <v>0.06491366864836964</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0.6024096385542168</v>
       </c>
       <c r="C85" t="n">
-        <v>0.05364320220684404</v>
+        <v>0.06402797480844229</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0.5952380952380952</v>
       </c>
       <c r="C86" t="n">
-        <v>0.05281867904761301</v>
+        <v>0.06293822096200202</v>
       </c>
     </row>
     <row r="87">
@@ -1388,7 +1388,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="C87" t="n">
-        <v>0.05191281216208919</v>
+        <v>0.06225481945181548</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0.5813953488372093</v>
       </c>
       <c r="C88" t="n">
-        <v>0.05096347768463434</v>
+        <v>0.06128388439769331</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0.5747126436781609</v>
       </c>
       <c r="C89" t="n">
-        <v>0.05037593306986533</v>
+        <v>0.05999841487062307</v>
       </c>
     </row>
     <row r="90">
@@ -1421,7 +1421,7 @@
         <v>0.5681818181818182</v>
       </c>
       <c r="C90" t="n">
-        <v>0.04963863580275805</v>
+        <v>0.05844201142666201</v>
       </c>
     </row>
     <row r="91">
@@ -1432,7 +1432,7 @@
         <v>0.5617977528089888</v>
       </c>
       <c r="C91" t="n">
-        <v>0.04872672880105441</v>
+        <v>0.05667135682226239</v>
       </c>
     </row>
     <row r="92">
@@ -1443,7 +1443,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C92" t="n">
-        <v>0.04760182585152947</v>
+        <v>0.05472938719446952</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0.5494505494505494</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04632010887223694</v>
+        <v>0.05276149694386311</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
         <v>0.5434782608695652</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0453682245910501</v>
+        <v>0.051296524027627</v>
       </c>
     </row>
     <row r="95">
@@ -1476,7 +1476,7 @@
         <v>0.5376344086021505</v>
       </c>
       <c r="C95" t="n">
-        <v>0.04437455712236311</v>
+        <v>0.04974902244345498</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0.5319148936170213</v>
       </c>
       <c r="C96" t="n">
-        <v>0.04329691314402276</v>
+        <v>0.04814673963887335</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="C97" t="n">
-        <v>0.04295308657095803</v>
+        <v>0.04651527167300028</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="C98" t="n">
-        <v>0.04278041733350447</v>
+        <v>0.04487872343919539</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0.5154639175257733</v>
       </c>
       <c r="C99" t="n">
-        <v>0.04248485355118495</v>
+        <v>0.04325781753903894</v>
       </c>
     </row>
     <row r="100">
@@ -1531,7 +1531,7 @@
         <v>0.5102040816326531</v>
       </c>
       <c r="C100" t="n">
-        <v>0.04204834091460481</v>
+        <v>0.04166983858548681</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0.5050505050505051</v>
       </c>
       <c r="C101" t="n">
-        <v>0.04146127156568622</v>
+        <v>0.04012872878051785</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="C102" t="n">
-        <v>0.04072168003451009</v>
+        <v>0.03877414710184015</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0.495049504950495</v>
       </c>
       <c r="C103" t="n">
-        <v>0.03984349086380241</v>
+        <v>0.03757012619749604</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0.4901960784313725</v>
       </c>
       <c r="C104" t="n">
-        <v>0.03918028695322383</v>
+        <v>0.03674176538828777</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0.4854368932038835</v>
       </c>
       <c r="C105" t="n">
-        <v>0.03836955953260526</v>
+        <v>0.03591765831769211</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0.4807692307692307</v>
       </c>
       <c r="C106" t="n">
-        <v>0.03742615712650233</v>
+        <v>0.03509450179680118</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="C107" t="n">
-        <v>0.03637495198409297</v>
+        <v>0.03427496838138953</v>
       </c>
     </row>
     <row r="108">
@@ -1619,7 +1619,7 @@
         <v>0.4716981132075471</v>
       </c>
       <c r="C108" t="n">
-        <v>0.03526765708776768</v>
+        <v>0.03370030741890316</v>
       </c>
     </row>
     <row r="109">
@@ -1630,7 +1630,7 @@
         <v>0.4672897196261682</v>
       </c>
       <c r="C109" t="n">
-        <v>0.03411460796031124</v>
+        <v>0.03335668021553075</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0.4629629629629629</v>
       </c>
       <c r="C110" t="n">
-        <v>0.032944747919026</v>
+        <v>0.03295345594431521</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0.4587155963302752</v>
       </c>
       <c r="C111" t="n">
-        <v>0.03200832876094005</v>
+        <v>0.03265238446691406</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="C112" t="n">
-        <v>0.03105055545846217</v>
+        <v>0.03228838167944028</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0.4504504504504504</v>
       </c>
       <c r="C113" t="n">
-        <v>0.03013946167466795</v>
+        <v>0.03190158329049811</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0.4464285714285714</v>
       </c>
       <c r="C114" t="n">
-        <v>0.02926798760592771</v>
+        <v>0.03147770445076524</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0.4424778761061947</v>
       </c>
       <c r="C115" t="n">
-        <v>0.0287920732039761</v>
+        <v>0.03108004745344002</v>
       </c>
     </row>
     <row r="116">
@@ -1707,7 +1707,7 @@
         <v>0.4385964912280702</v>
       </c>
       <c r="C116" t="n">
-        <v>0.02853190531614525</v>
+        <v>0.03078573592908396</v>
       </c>
     </row>
     <row r="117">
@@ -1718,7 +1718,7 @@
         <v>0.4347826086956521</v>
       </c>
       <c r="C117" t="n">
-        <v>0.02820138269264248</v>
+        <v>0.03047495613095571</v>
       </c>
     </row>
     <row r="118">
@@ -1729,7 +1729,7 @@
         <v>0.4310344827586207</v>
       </c>
       <c r="C118" t="n">
-        <v>0.02781436869425227</v>
+        <v>0.03016180129346879</v>
       </c>
     </row>
     <row r="119">
@@ -1740,7 +1740,7 @@
         <v>0.4273504273504274</v>
       </c>
       <c r="C119" t="n">
-        <v>0.02758005677177168</v>
+        <v>0.03015087588211144</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0.4237288135593221</v>
       </c>
       <c r="C120" t="n">
-        <v>0.02732089798892236</v>
+        <v>0.03024060656518718</v>
       </c>
     </row>
     <row r="121">
@@ -1762,7 +1762,7 @@
         <v>0.4201680672268908</v>
       </c>
       <c r="C121" t="n">
-        <v>0.02703528735664602</v>
+        <v>0.03031035733255058</v>
       </c>
     </row>
     <row r="122">
@@ -1773,7 +1773,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="C122" t="n">
-        <v>0.02673100962448337</v>
+        <v>0.03035714982918889</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0.4132231404958678</v>
       </c>
       <c r="C123" t="n">
-        <v>0.02648998198360383</v>
+        <v>0.03037830600294113</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0.4098360655737705</v>
       </c>
       <c r="C124" t="n">
-        <v>0.02624504280355892</v>
+        <v>0.03037151970912708</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0.4065040650406504</v>
       </c>
       <c r="C125" t="n">
-        <v>0.02610170076253928</v>
+        <v>0.0303794543366807</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0.4032258064516129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.02627521644849455</v>
+        <v>0.03045370107329187</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0.4</v>
       </c>
       <c r="C127" t="n">
-        <v>0.02642119958949407</v>
+        <v>0.03072949339402812</v>
       </c>
     </row>
     <row r="128">
@@ -1839,7 +1839,7 @@
         <v>0.3968253968253968</v>
       </c>
       <c r="C128" t="n">
-        <v>0.02656700269375996</v>
+        <v>0.03105284967754251</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0.3937007874015748</v>
       </c>
       <c r="C129" t="n">
-        <v>0.02672104637235547</v>
+        <v>0.03140068049935795</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0.390625</v>
       </c>
       <c r="C130" t="n">
-        <v>0.02684567584991845</v>
+        <v>0.03174403789961967</v>
       </c>
     </row>
     <row r="131">
@@ -1872,7 +1872,7 @@
         <v>0.3875968992248062</v>
       </c>
       <c r="C131" t="n">
-        <v>0.02693066921290891</v>
+        <v>0.03207021882154948</v>
       </c>
     </row>
     <row r="132">
@@ -1883,7 +1883,7 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="C132" t="n">
-        <v>0.02697352755452306</v>
+        <v>0.03236696716879959</v>
       </c>
     </row>
     <row r="133">
@@ -1894,7 +1894,7 @@
         <v>0.3816793893129771</v>
       </c>
       <c r="C133" t="n">
-        <v>0.02697283136392679</v>
+        <v>0.0326231999829345</v>
       </c>
     </row>
     <row r="134">
@@ -1905,7 +1905,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>0.02694461414662506</v>
+        <v>0.03285050185057133</v>
       </c>
     </row>
     <row r="135">
@@ -1916,7 +1916,7 @@
         <v>0.3759398496240601</v>
       </c>
       <c r="C135" t="n">
-        <v>0.02688384942873377</v>
+        <v>0.03303296509311365</v>
       </c>
     </row>
     <row r="136">
@@ -1927,7 +1927,7 @@
         <v>0.3731343283582089</v>
       </c>
       <c r="C136" t="n">
-        <v>0.02678377560128531</v>
+        <v>0.03315397542732025</v>
       </c>
     </row>
     <row r="137">
@@ -1938,7 +1938,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="C137" t="n">
-        <v>0.02665284549560372</v>
+        <v>0.03320890945342266</v>
       </c>
     </row>
     <row r="138">
@@ -1949,7 +1949,7 @@
         <v>0.3676470588235294</v>
       </c>
       <c r="C138" t="n">
-        <v>0.0265429744457933</v>
+        <v>0.03319508991975308</v>
       </c>
     </row>
     <row r="139">
@@ -1960,7 +1960,7 @@
         <v>0.364963503649635</v>
       </c>
       <c r="C139" t="n">
-        <v>0.02650829719158489</v>
+        <v>0.03311324642261133</v>
       </c>
     </row>
     <row r="140">
@@ -1971,7 +1971,7 @@
         <v>0.3623188405797101</v>
       </c>
       <c r="C140" t="n">
-        <v>0.02642342510992816</v>
+        <v>0.03296570328661991</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0.3597122302158273</v>
       </c>
       <c r="C141" t="n">
-        <v>0.02629187196559281</v>
+        <v>0.03275211198851174</v>
       </c>
     </row>
     <row r="142">
@@ -1993,7 +1993,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="C142" t="n">
-        <v>0.02611728066564173</v>
+        <v>0.03252245201897921</v>
       </c>
     </row>
     <row r="143">
@@ -2004,7 +2004,7 @@
         <v>0.3546099290780142</v>
       </c>
       <c r="C143" t="n">
-        <v>0.02590440976839615</v>
+        <v>0.03231031481120101</v>
       </c>
     </row>
     <row r="144">
@@ -2015,7 +2015,7 @@
         <v>0.3521126760563381</v>
       </c>
       <c r="C144" t="n">
-        <v>0.02565698701950454</v>
+        <v>0.0321661961045081</v>
       </c>
     </row>
     <row r="145">
@@ -2026,7 +2026,7 @@
         <v>0.3496503496503497</v>
       </c>
       <c r="C145" t="n">
-        <v>0.02537901735522518</v>
+        <v>0.03199622512660594</v>
       </c>
     </row>
     <row r="146">
@@ -2037,7 +2037,7 @@
         <v>0.3472222222222222</v>
       </c>
       <c r="C146" t="n">
-        <v>0.02513777175084154</v>
+        <v>0.03178847838146619</v>
       </c>
     </row>
     <row r="147">
@@ -2048,7 +2048,7 @@
         <v>0.3448275862068966</v>
       </c>
       <c r="C147" t="n">
-        <v>0.02490782311910187</v>
+        <v>0.03154770378986913</v>
       </c>
     </row>
     <row r="148">
@@ -2059,7 +2059,7 @@
         <v>0.3424657534246575</v>
       </c>
       <c r="C148" t="n">
-        <v>0.02463909610420223</v>
+        <v>0.03132995986364875</v>
       </c>
     </row>
     <row r="149">
@@ -2070,7 +2070,7 @@
         <v>0.3401360544217687</v>
       </c>
       <c r="C149" t="n">
-        <v>0.02433614593339631</v>
+        <v>0.03114076895287307</v>
       </c>
     </row>
     <row r="150">
@@ -2081,7 +2081,7 @@
         <v>0.3378378378378378</v>
       </c>
       <c r="C150" t="n">
-        <v>0.02403964601860972</v>
+        <v>0.03100407596030006</v>
       </c>
     </row>
     <row r="151">
@@ -2092,7 +2092,7 @@
         <v>0.3355704697986577</v>
       </c>
       <c r="C151" t="n">
-        <v>0.02380473967346744</v>
+        <v>0.03094099843235183</v>
       </c>
     </row>
     <row r="152">
@@ -2103,7 +2103,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C152" t="n">
-        <v>0.02361602998641812</v>
+        <v>0.03089672637643759</v>
       </c>
     </row>
     <row r="153">
@@ -2114,7 +2114,7 @@
         <v>0.3311258278145696</v>
       </c>
       <c r="C153" t="n">
-        <v>0.02349256124639286</v>
+        <v>0.03085565009238238</v>
       </c>
     </row>
     <row r="154">
@@ -2125,7 +2125,7 @@
         <v>0.3289473684210527</v>
       </c>
       <c r="C154" t="n">
-        <v>0.02335211694609092</v>
+        <v>0.03075139899467356</v>
       </c>
     </row>
     <row r="155">
@@ -2136,7 +2136,7 @@
         <v>0.326797385620915</v>
       </c>
       <c r="C155" t="n">
-        <v>0.02320765057021774</v>
+        <v>0.03061932613229192</v>
       </c>
     </row>
     <row r="156">
@@ -2147,7 +2147,7 @@
         <v>0.3246753246753247</v>
       </c>
       <c r="C156" t="n">
-        <v>0.0232447985929842</v>
+        <v>0.03062158585911354</v>
       </c>
     </row>
     <row r="157">
@@ -2158,7 +2158,7 @@
         <v>0.3225806451612903</v>
       </c>
       <c r="C157" t="n">
-        <v>0.02325369189175141</v>
+        <v>0.03057710430773954</v>
       </c>
     </row>
     <row r="158">
@@ -2169,7 +2169,7 @@
         <v>0.3205128205128205</v>
       </c>
       <c r="C158" t="n">
-        <v>0.02343427267789741</v>
+        <v>0.03067491305147743</v>
       </c>
     </row>
     <row r="159">
@@ -2180,7 +2180,7 @@
         <v>0.3184713375796178</v>
       </c>
       <c r="C159" t="n">
-        <v>0.02360144151836771</v>
+        <v>0.0308594640295245</v>
       </c>
     </row>
     <row r="160">
@@ -2191,7 +2191,7 @@
         <v>0.3164556962025316</v>
       </c>
       <c r="C160" t="n">
-        <v>0.02369428369937472</v>
+        <v>0.03098112143167226</v>
       </c>
     </row>
     <row r="161">
@@ -2202,7 +2202,7 @@
         <v>0.3144654088050314</v>
       </c>
       <c r="C161" t="n">
-        <v>0.02375406731396561</v>
+        <v>0.03107331995729537</v>
       </c>
     </row>
     <row r="162">
@@ -2213,7 +2213,7 @@
         <v>0.3125</v>
       </c>
       <c r="C162" t="n">
-        <v>0.02377234673633661</v>
+        <v>0.03115160236967036</v>
       </c>
     </row>
     <row r="163">
@@ -2224,7 +2224,7 @@
         <v>0.3105590062111801</v>
       </c>
       <c r="C163" t="n">
-        <v>0.02371801519836325</v>
+        <v>0.03119414943379324</v>
       </c>
     </row>
     <row r="164">
@@ -2235,7 +2235,7 @@
         <v>0.308641975308642</v>
       </c>
       <c r="C164" t="n">
-        <v>0.02377025634106439</v>
+        <v>0.03134221948903284</v>
       </c>
     </row>
     <row r="165">
@@ -2246,7 +2246,7 @@
         <v>0.3067484662576687</v>
       </c>
       <c r="C165" t="n">
-        <v>0.02396958360139105</v>
+        <v>0.03163576993411901</v>
       </c>
     </row>
     <row r="166">
@@ -2257,7 +2257,7 @@
         <v>0.3048780487804878</v>
       </c>
       <c r="C166" t="n">
-        <v>0.02411629837266904</v>
+        <v>0.03187635958151305</v>
       </c>
     </row>
     <row r="167">
@@ -2268,7 +2268,7 @@
         <v>0.303030303030303</v>
       </c>
       <c r="C167" t="n">
-        <v>0.02420547383152709</v>
+        <v>0.03205682709566642</v>
       </c>
     </row>
     <row r="168">
@@ -2279,7 +2279,7 @@
         <v>0.3012048192771084</v>
       </c>
       <c r="C168" t="n">
-        <v>0.02423717882021405</v>
+        <v>0.03217670586436942</v>
       </c>
     </row>
     <row r="169">
@@ -2290,7 +2290,7 @@
         <v>0.2994011976047904</v>
       </c>
       <c r="C169" t="n">
-        <v>0.02421359523563335</v>
+        <v>0.03223782784240205</v>
       </c>
     </row>
     <row r="170">
@@ -2301,7 +2301,7 @@
         <v>0.2976190476190476</v>
       </c>
       <c r="C170" t="n">
-        <v>0.02413295970805808</v>
+        <v>0.03223934079130972</v>
       </c>
     </row>
     <row r="171">
@@ -2312,7 +2312,7 @@
         <v>0.2958579881656805</v>
       </c>
       <c r="C171" t="n">
-        <v>0.0239983051273583</v>
+        <v>0.03218220387117748</v>
       </c>
     </row>
     <row r="172">
@@ -2323,7 +2323,7 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="C172" t="n">
-        <v>0.02381223701804618</v>
+        <v>0.03206796339950296</v>
       </c>
     </row>
     <row r="173">
@@ -2334,7 +2334,7 @@
         <v>0.2923976608187134</v>
       </c>
       <c r="C173" t="n">
-        <v>0.02366700871135703</v>
+        <v>0.03199247537577922</v>
       </c>
     </row>
     <row r="174">
@@ -2345,7 +2345,7 @@
         <v>0.2906976744186047</v>
       </c>
       <c r="C174" t="n">
-        <v>0.02356940374216012</v>
+        <v>0.03199519270314022</v>
       </c>
     </row>
     <row r="175">
@@ -2356,7 +2356,7 @@
         <v>0.2890173410404624</v>
       </c>
       <c r="C175" t="n">
-        <v>0.02346979974488341</v>
+        <v>0.03198449855580881</v>
       </c>
     </row>
     <row r="176">
@@ -2367,7 +2367,7 @@
         <v>0.2873563218390804</v>
       </c>
       <c r="C176" t="n">
-        <v>0.02332122586136137</v>
+        <v>0.03191328699404703</v>
       </c>
     </row>
     <row r="177">
@@ -2378,7 +2378,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="C177" t="n">
-        <v>0.02319738181892336</v>
+        <v>0.0318547224350491</v>
       </c>
     </row>
     <row r="178">
@@ -2389,7 +2389,7 @@
         <v>0.2840909090909091</v>
       </c>
       <c r="C178" t="n">
-        <v>0.02320899193046438</v>
+        <v>0.03190986480535177</v>
       </c>
     </row>
     <row r="179">
@@ -2400,7 +2400,7 @@
         <v>0.2824858757062147</v>
       </c>
       <c r="C179" t="n">
-        <v>0.02318378112267188</v>
+        <v>0.03191362181379</v>
       </c>
     </row>
     <row r="180">
@@ -2411,7 +2411,7 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="C180" t="n">
-        <v>0.02324262694489326</v>
+        <v>0.03198704939620167</v>
       </c>
     </row>
     <row r="181">
@@ -2422,7 +2422,7 @@
         <v>0.2793296089385475</v>
       </c>
       <c r="C181" t="n">
-        <v>0.02327171060717691</v>
+        <v>0.03201501925823756</v>
       </c>
     </row>
     <row r="182">
@@ -2433,7 +2433,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="C182" t="n">
-        <v>0.02326536239866496</v>
+        <v>0.03199096109799471</v>
       </c>
     </row>
     <row r="183">
@@ -2444,7 +2444,7 @@
         <v>0.2762430939226519</v>
       </c>
       <c r="C183" t="n">
-        <v>0.02324292955330036</v>
+        <v>0.0319336576904178</v>
       </c>
     </row>
     <row r="184">
@@ -2455,7 +2455,7 @@
         <v>0.2747252747252747</v>
       </c>
       <c r="C184" t="n">
-        <v>0.0231891278685453</v>
+        <v>0.03182783567377272</v>
       </c>
     </row>
     <row r="185">
@@ -2466,7 +2466,7 @@
         <v>0.273224043715847</v>
       </c>
       <c r="C185" t="n">
-        <v>0.02309662328199154</v>
+        <v>0.03185246482305009</v>
       </c>
     </row>
     <row r="186">
@@ -2477,7 +2477,7 @@
         <v>0.2717391304347826</v>
       </c>
       <c r="C186" t="n">
-        <v>0.0229694763554746</v>
+        <v>0.03184962726263346</v>
       </c>
     </row>
     <row r="187">
@@ -2488,7 +2488,7 @@
         <v>0.2702702702702702</v>
       </c>
       <c r="C187" t="n">
-        <v>0.02280763961875705</v>
+        <v>0.03182209587781579</v>
       </c>
     </row>
     <row r="188">
@@ -2499,7 +2499,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="C188" t="n">
-        <v>0.02261201081590363</v>
+        <v>0.03175821864001701</v>
       </c>
     </row>
     <row r="189">
@@ -2510,7 +2510,7 @@
         <v>0.267379679144385</v>
       </c>
       <c r="C189" t="n">
-        <v>0.02240702130914101</v>
+        <v>0.03164324544602241</v>
       </c>
     </row>
     <row r="190">
@@ -2521,7 +2521,7 @@
         <v>0.2659574468085106</v>
       </c>
       <c r="C190" t="n">
-        <v>0.02217673196277619</v>
+        <v>0.03147885393143988</v>
       </c>
     </row>
     <row r="191">
@@ -2532,7 +2532,7 @@
         <v>0.2645502645502645</v>
       </c>
       <c r="C191" t="n">
-        <v>0.02196383470050208</v>
+        <v>0.03130876146258879</v>
       </c>
     </row>
     <row r="192">
@@ -2543,7 +2543,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="C192" t="n">
-        <v>0.02181198915373342</v>
+        <v>0.03117573200780201</v>
       </c>
     </row>
     <row r="193">
@@ -2554,7 +2554,7 @@
         <v>0.2617801047120419</v>
       </c>
       <c r="C193" t="n">
-        <v>0.02163509473553273</v>
+        <v>0.03110827653268054</v>
       </c>
     </row>
     <row r="194">
@@ -2565,7 +2565,7 @@
         <v>0.2604166666666667</v>
       </c>
       <c r="C194" t="n">
-        <v>0.02143475629018325</v>
+        <v>0.03109669710546206</v>
       </c>
     </row>
     <row r="195">
@@ -2576,7 +2576,7 @@
         <v>0.2590673575129534</v>
       </c>
       <c r="C195" t="n">
-        <v>0.02124914557589814</v>
+        <v>0.03107333724939045</v>
       </c>
     </row>
     <row r="196">
@@ -2587,7 +2587,7 @@
         <v>0.2577319587628866</v>
       </c>
       <c r="C196" t="n">
-        <v>0.02104391222080781</v>
+        <v>0.03100273996431428</v>
       </c>
     </row>
     <row r="197">
@@ -2598,7 +2598,7 @@
         <v>0.2564102564102564</v>
       </c>
       <c r="C197" t="n">
-        <v>0.02082131406371187</v>
+        <v>0.03089437555367764</v>
       </c>
     </row>
     <row r="198">
@@ -2609,7 +2609,7 @@
         <v>0.2551020408163265</v>
       </c>
       <c r="C198" t="n">
-        <v>0.0205829683665515</v>
+        <v>0.03074795819543992</v>
       </c>
     </row>
     <row r="199">
@@ -2620,7 +2620,7 @@
         <v>0.2538071065989848</v>
       </c>
       <c r="C199" t="n">
-        <v>0.020329352668713</v>
+        <v>0.03056028219400993</v>
       </c>
     </row>
     <row r="200">
@@ -2631,7 +2631,7 @@
         <v>0.2525252525252525</v>
       </c>
       <c r="C200" t="n">
-        <v>0.02006188140554565</v>
+        <v>0.03033329477587256</v>
       </c>
     </row>
     <row r="201">
@@ -2642,7 +2642,7 @@
         <v>0.2512562814070352</v>
       </c>
       <c r="C201" t="n">
-        <v>0.01978749832109078</v>
+        <v>0.03006672613490708</v>
       </c>
     </row>
     <row r="202">
@@ -2653,7 +2653,7 @@
         <v>0.25</v>
       </c>
       <c r="C202" t="n">
-        <v>0.01951190270252014</v>
+        <v>0.02976312847752873</v>
       </c>
     </row>
   </sheetData>
